--- a/data/Dataset_other_taxa.xlsx
+++ b/data/Dataset_other_taxa.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2b0679614ff64932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rade972a251df48eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,10 +43,17 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -121,6 +128,23 @@
     </x:indexedColors>
   </x:colors>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -357,109 +381,105 @@
       </x:c>
       <x:c r="D1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">remeshing_parameter</x:t>
+          <x:t xml:space="preserve">length_x</x:t>
         </x:is>
       </x:c>
       <x:c r="E1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">length_x</x:t>
+          <x:t xml:space="preserve">width_y</x:t>
         </x:is>
       </x:c>
       <x:c r="F1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">width_y</x:t>
+          <x:t xml:space="preserve">height_z</x:t>
         </x:is>
       </x:c>
       <x:c r="G1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">height_z</x:t>
+          <x:t xml:space="preserve">orbit_patch</x:t>
         </x:is>
       </x:c>
       <x:c r="H1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">orbit_patch</x:t>
+          <x:t xml:space="preserve">orbit_inliers</x:t>
         </x:is>
       </x:c>
       <x:c r="I1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">orbit_inliers</x:t>
+          <x:t xml:space="preserve">fit_error_pct</x:t>
         </x:is>
       </x:c>
       <x:c r="J1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">fit_error_pct</x:t>
+          <x:t xml:space="preserve">sphere_radius</x:t>
         </x:is>
       </x:c>
       <x:c r="K1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sphere_radius</x:t>
+          <x:t xml:space="preserve">curvature</x:t>
         </x:is>
       </x:c>
       <x:c r="L1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">curvature</x:t>
+          <x:t xml:space="preserve">sphere_center_x</x:t>
         </x:is>
       </x:c>
       <x:c r="M1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sphere_center_x</x:t>
+          <x:t xml:space="preserve">sphere_center_y</x:t>
         </x:is>
       </x:c>
       <x:c r="N1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sphere_center_y</x:t>
+          <x:t xml:space="preserve">sphere_center_z</x:t>
         </x:is>
       </x:c>
       <x:c r="O1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sphere_center_z</x:t>
+          <x:t xml:space="preserve">sphere_center_along_pct</x:t>
         </x:is>
       </x:c>
       <x:c r="P1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sphere_center_along_pct</x:t>
+          <x:t xml:space="preserve">reliable</x:t>
         </x:is>
       </x:c>
       <x:c r="Q1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">reliable</x:t>
+          <x:t xml:space="preserve">flag_reason</x:t>
         </x:is>
       </x:c>
       <x:c r="R1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flag_reason</x:t>
+          <x:t xml:space="preserve">second_sphere_radius</x:t>
         </x:is>
       </x:c>
       <x:c r="S1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">second_sphere_radius</x:t>
+          <x:t xml:space="preserve">second_orbit_inliers</x:t>
         </x:is>
       </x:c>
       <x:c r="T1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">second_orbit_inliers</x:t>
+          <x:t xml:space="preserve">second_fit_error_pct</x:t>
         </x:is>
       </x:c>
       <x:c r="U1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">second_fit_error_pct</x:t>
+          <x:t xml:space="preserve">closed</x:t>
         </x:is>
       </x:c>
       <x:c r="V1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">closed</x:t>
+          <x:t xml:space="preserve">n_components</x:t>
         </x:is>
       </x:c>
       <x:c r="W1" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">n_components</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="X1" s="1" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">genus_largest</x:t>
         </x:is>
       </x:c>
+      <x:c r="X1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="inlineStr">
@@ -478,62 +498,60 @@
         </x:is>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>60</x:v>
+        <x:v>27.45293617248535</x:v>
       </x:c>
       <x:c r="E2" t="n">
-        <x:v>27.45293617248535</x:v>
+        <x:v>14.12081670761108</x:v>
       </x:c>
       <x:c r="F2" t="n">
-        <x:v>14.12081670761108</x:v>
+        <x:v>12.48340559005737</x:v>
       </x:c>
       <x:c r="G2" t="n">
-        <x:v>12.48340559005737</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H2" t="n">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I2" t="n">
-        <x:v>83</x:v>
+        <x:v>5.156992825337751</x:v>
       </x:c>
       <x:c r="J2" t="n">
-        <x:v>5.156992825337751</x:v>
+        <x:v>2.702948117904689</x:v>
       </x:c>
       <x:c r="K2" t="n">
-        <x:v>2.702948117904689</x:v>
+        <x:v>0.3699664057093315</x:v>
       </x:c>
       <x:c r="L2" t="n">
-        <x:v>0.3699664057093315</x:v>
+        <x:v>-3.136544522046603</x:v>
       </x:c>
       <x:c r="M2" t="n">
-        <x:v>-3.136544522046603</x:v>
+        <x:v>-3.039248542453103</x:v>
       </x:c>
       <x:c r="N2" t="n">
-        <x:v>-3.039248542453103</x:v>
+        <x:v>1.731111050435127</x:v>
       </x:c>
       <x:c r="O2" t="n">
-        <x:v>1.731111050435127</x:v>
-      </x:c>
-      <x:c r="P2" t="n">
         <x:v>54.57306080474022</x:v>
       </x:c>
-      <x:c r="Q2" t="inlineStr">
+      <x:c r="P2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q2"/>
       <x:c r="R2"/>
       <x:c r="S2"/>
       <x:c r="T2"/>
-      <x:c r="U2"/>
-      <x:c r="V2" t="b">
-        <x:v>1</x:v>
+      <x:c r="U2" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V2" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="inlineStr">
@@ -552,68 +570,66 @@
         </x:is>
       </x:c>
       <x:c r="D3" t="n">
+        <x:v>31.50770378112793</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>16.33395576477051</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>14.53167390823364</x:v>
+      </x:c>
+      <x:c r="G3" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E3" t="n">
-        <x:v>31.50770378112793</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
-        <x:v>16.33395576477051</x:v>
-      </x:c>
-      <x:c r="G3" t="n">
-        <x:v>14.53167390823364</x:v>
-      </x:c>
       <x:c r="H3" t="n">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I3" t="n">
-        <x:v>51</x:v>
+        <x:v>4.102079722864959</x:v>
       </x:c>
       <x:c r="J3" t="n">
-        <x:v>4.102079722864959</x:v>
+        <x:v>3.815219355861561</x:v>
       </x:c>
       <x:c r="K3" t="n">
-        <x:v>3.815219355861561</x:v>
+        <x:v>0.2621081271417952</x:v>
       </x:c>
       <x:c r="L3" t="n">
-        <x:v>0.2621081271417952</x:v>
+        <x:v>-4.808380148671626</x:v>
       </x:c>
       <x:c r="M3" t="n">
-        <x:v>-4.808380148671626</x:v>
+        <x:v>-4.136044327730033</x:v>
       </x:c>
       <x:c r="N3" t="n">
-        <x:v>-4.136044327730033</x:v>
+        <x:v>0.8349791883522092</x:v>
       </x:c>
       <x:c r="O3" t="n">
-        <x:v>0.8349791883522092</x:v>
-      </x:c>
-      <x:c r="P3" t="n">
         <x:v>51.53807604182363</x:v>
       </x:c>
-      <x:c r="Q3" t="inlineStr">
+      <x:c r="P3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3" t="n">
+        <x:v>2.951187426901858</x:v>
+      </x:c>
       <x:c r="S3" t="n">
-        <x:v>2.951187426901858</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="T3" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="U3" t="n">
         <x:v>7.987575724653116</x:v>
       </x:c>
-      <x:c r="V3" t="b">
+      <x:c r="U3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="inlineStr">
@@ -632,62 +648,60 @@
         </x:is>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>40</x:v>
+        <x:v>33.16012668609619</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>33.16012668609619</x:v>
+        <x:v>17.14799833297729</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>17.14799833297729</x:v>
+        <x:v>15.1051812171936</x:v>
       </x:c>
       <x:c r="G4" t="n">
-        <x:v>15.1051812171936</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H4" t="n">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I4" t="n">
-        <x:v>41</x:v>
+        <x:v>2.537069613147969</x:v>
       </x:c>
       <x:c r="J4" t="n">
-        <x:v>2.537069613147969</x:v>
+        <x:v>3.144255722153282</x:v>
       </x:c>
       <x:c r="K4" t="n">
-        <x:v>3.144255722153282</x:v>
+        <x:v>0.3180402894568542</x:v>
       </x:c>
       <x:c r="L4" t="n">
-        <x:v>0.3180402894568542</x:v>
+        <x:v>-3.480817727652493</x:v>
       </x:c>
       <x:c r="M4" t="n">
-        <x:v>-3.480817727652493</x:v>
+        <x:v>-3.578571688762909</x:v>
       </x:c>
       <x:c r="N4" t="n">
-        <x:v>-3.578571688762909</x:v>
+        <x:v>1.432208047124235</x:v>
       </x:c>
       <x:c r="O4" t="n">
-        <x:v>1.432208047124235</x:v>
-      </x:c>
-      <x:c r="P4" t="n">
         <x:v>55.34926871321745</x:v>
       </x:c>
-      <x:c r="Q4" t="inlineStr">
+      <x:c r="P4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q4"/>
       <x:c r="R4"/>
       <x:c r="S4"/>
       <x:c r="T4"/>
-      <x:c r="U4"/>
-      <x:c r="V4" t="b">
+      <x:c r="U4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X4" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
@@ -706,68 +720,66 @@
         </x:is>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>59</x:v>
+        <x:v>32.07593727111816</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>32.07593727111816</x:v>
+        <x:v>16.20369338989258</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>16.20369338989258</x:v>
+        <x:v>14.45343637466431</x:v>
       </x:c>
       <x:c r="G5" t="n">
-        <x:v>14.45343637466431</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H5" t="n">
-        <x:v>79</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I5" t="n">
-        <x:v>71</x:v>
+        <x:v>5.578936992620412</x:v>
       </x:c>
       <x:c r="J5" t="n">
-        <x:v>5.578936992620412</x:v>
+        <x:v>2.893393537574992</x:v>
       </x:c>
       <x:c r="K5" t="n">
-        <x:v>2.893393537574992</x:v>
+        <x:v>0.3456149282887108</x:v>
       </x:c>
       <x:c r="L5" t="n">
-        <x:v>0.3456149282887108</x:v>
+        <x:v>-2.796745948788197</x:v>
       </x:c>
       <x:c r="M5" t="n">
-        <x:v>-2.796745948788197</x:v>
+        <x:v>3.62148758516704</x:v>
       </x:c>
       <x:c r="N5" t="n">
-        <x:v>3.62148758516704</x:v>
+        <x:v>0.3718973595202951</x:v>
       </x:c>
       <x:c r="O5" t="n">
-        <x:v>0.3718973595202951</x:v>
-      </x:c>
-      <x:c r="P5" t="n">
         <x:v>57.39859674382279</x:v>
       </x:c>
-      <x:c r="Q5" t="inlineStr">
+      <x:c r="P5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R5"/>
+      <x:c r="Q5"/>
+      <x:c r="R5" t="n">
+        <x:v>3.247672490294248</x:v>
+      </x:c>
       <x:c r="S5" t="n">
-        <x:v>3.247672490294248</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T5" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="U5" t="n">
         <x:v>3.353516253735482</x:v>
       </x:c>
-      <x:c r="V5" t="b">
+      <x:c r="U5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V5" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X5" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="inlineStr">
@@ -786,72 +798,70 @@
         </x:is>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>55</x:v>
+        <x:v>33.28346633911133</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:v>33.28346633911133</x:v>
+        <x:v>16.72253799438477</x:v>
       </x:c>
       <x:c r="F6" t="n">
-        <x:v>16.72253799438477</x:v>
+        <x:v>14.0156455039978</x:v>
       </x:c>
       <x:c r="G6" t="n">
-        <x:v>14.0156455039978</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H6" t="n">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I6" t="n">
-        <x:v>29</x:v>
+        <x:v>5.009122408768981</x:v>
       </x:c>
       <x:c r="J6" t="n">
-        <x:v>5.009122408768981</x:v>
+        <x:v>4.649859785374105</x:v>
       </x:c>
       <x:c r="K6" t="n">
-        <x:v>4.649859785374105</x:v>
+        <x:v>0.2150602482994108</x:v>
       </x:c>
       <x:c r="L6" t="n">
-        <x:v>0.2150602482994108</x:v>
+        <x:v>-3.708133190090563</x:v>
       </x:c>
       <x:c r="M6" t="n">
-        <x:v>-3.708133190090563</x:v>
+        <x:v>7.892802864244872</x:v>
       </x:c>
       <x:c r="N6" t="n">
-        <x:v>7.892802864244872</x:v>
+        <x:v>2.160208218427538</x:v>
       </x:c>
       <x:c r="O6" t="n">
-        <x:v>2.160208218427538</x:v>
-      </x:c>
-      <x:c r="P6" t="n">
         <x:v>54.31720916354509</x:v>
       </x:c>
+      <x:c r="P6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q6" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R6" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fewer than 40 inliers</x:t>
         </x:is>
       </x:c>
+      <x:c r="R6" t="n">
+        <x:v>5.10171473054285</x:v>
+      </x:c>
       <x:c r="S6" t="n">
-        <x:v>5.10171473054285</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="T6" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="U6" t="n">
         <x:v>2.441857425191271</x:v>
       </x:c>
-      <x:c r="V6" t="b">
+      <x:c r="U6" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V6" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="inlineStr">
@@ -870,68 +880,66 @@
         </x:is>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>45</x:v>
+        <x:v>31.4043664932251</x:v>
       </x:c>
       <x:c r="E7" t="n">
-        <x:v>31.4043664932251</x:v>
+        <x:v>16.3531322479248</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>16.3531322479248</x:v>
+        <x:v>13.64091300964355</x:v>
       </x:c>
       <x:c r="G7" t="n">
-        <x:v>13.64091300964355</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H7" t="n">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I7" t="n">
-        <x:v>51</x:v>
+        <x:v>4.145466779047198</x:v>
       </x:c>
       <x:c r="J7" t="n">
-        <x:v>4.145466779047198</x:v>
+        <x:v>2.590545813852626</x:v>
       </x:c>
       <x:c r="K7" t="n">
-        <x:v>2.590545813852626</x:v>
+        <x:v>0.386019036858033</x:v>
       </x:c>
       <x:c r="L7" t="n">
-        <x:v>0.386019036858033</x:v>
+        <x:v>-0.7363641307109089</x:v>
       </x:c>
       <x:c r="M7" t="n">
-        <x:v>-0.7363641307109089</x:v>
+        <x:v>-2.742158021313817</x:v>
       </x:c>
       <x:c r="N7" t="n">
-        <x:v>-2.742158021313817</x:v>
+        <x:v>2.175709859193494</x:v>
       </x:c>
       <x:c r="O7" t="n">
-        <x:v>2.175709859193494</x:v>
-      </x:c>
-      <x:c r="P7" t="n">
         <x:v>55.36503792310013</x:v>
       </x:c>
-      <x:c r="Q7" t="inlineStr">
+      <x:c r="P7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R7"/>
+      <x:c r="Q7"/>
+      <x:c r="R7" t="n">
+        <x:v>2.851188277762256</x:v>
+      </x:c>
       <x:c r="S7" t="n">
-        <x:v>2.851188277762256</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="T7" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="U7" t="n">
         <x:v>2.587884372938401</x:v>
       </x:c>
-      <x:c r="V7" t="b">
+      <x:c r="U7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V7" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X7" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="inlineStr">
@@ -950,66 +958,64 @@
         </x:is>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>60</x:v>
+        <x:v>29.23043251037598</x:v>
       </x:c>
       <x:c r="E8" t="n">
-        <x:v>29.23043251037598</x:v>
+        <x:v>15.0567421913147</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>15.0567421913147</x:v>
+        <x:v>12.77620124816895</x:v>
       </x:c>
       <x:c r="G8" t="n">
-        <x:v>12.77620124816895</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H8" t="n">
-        <x:v>151</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I8" t="n">
-        <x:v>129</x:v>
+        <x:v>17.58862870469764</x:v>
       </x:c>
       <x:c r="J8" t="n">
-        <x:v>17.58862870469764</x:v>
+        <x:v>2.849045544039879</x:v>
       </x:c>
       <x:c r="K8" t="n">
-        <x:v>2.849045544039879</x:v>
+        <x:v>0.3509947400075689</x:v>
       </x:c>
       <x:c r="L8" t="n">
-        <x:v>0.3509947400075689</x:v>
+        <x:v>-3.664230788984375</x:v>
       </x:c>
       <x:c r="M8" t="n">
-        <x:v>-3.664230788984375</x:v>
+        <x:v>-2.718223365596234</x:v>
       </x:c>
       <x:c r="N8" t="n">
-        <x:v>-2.718223365596234</x:v>
+        <x:v>1.632729561372315</x:v>
       </x:c>
       <x:c r="O8" t="n">
-        <x:v>1.632729561372315</x:v>
-      </x:c>
-      <x:c r="P8" t="n">
         <x:v>58.04852847003578</x:v>
       </x:c>
+      <x:c r="P8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R8" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fit error above 10% of the radius</x:t>
         </x:is>
       </x:c>
+      <x:c r="R8"/>
       <x:c r="S8"/>
       <x:c r="T8"/>
-      <x:c r="U8"/>
-      <x:c r="V8" t="b">
+      <x:c r="U8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X8" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="inlineStr">
@@ -1028,68 +1034,66 @@
         </x:is>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>40</x:v>
+        <x:v>26.86209774017334</x:v>
       </x:c>
       <x:c r="E9" t="n">
-        <x:v>26.86209774017334</x:v>
+        <x:v>14.07776117324829</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>14.07776117324829</x:v>
+        <x:v>13.60973596572876</x:v>
       </x:c>
       <x:c r="G9" t="n">
-        <x:v>13.60973596572876</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H9" t="n">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I9" t="n">
-        <x:v>84</x:v>
+        <x:v>7.83282603759594</x:v>
       </x:c>
       <x:c r="J9" t="n">
-        <x:v>7.83282603759594</x:v>
+        <x:v>2.594712813200912</x:v>
       </x:c>
       <x:c r="K9" t="n">
-        <x:v>2.594712813200912</x:v>
+        <x:v>0.3853991065648499</x:v>
       </x:c>
       <x:c r="L9" t="n">
-        <x:v>0.3853991065648499</x:v>
+        <x:v>-2.773836890710649</x:v>
       </x:c>
       <x:c r="M9" t="n">
-        <x:v>-2.773836890710649</x:v>
+        <x:v>4.427864268093141</x:v>
       </x:c>
       <x:c r="N9" t="n">
-        <x:v>4.427864268093141</x:v>
+        <x:v>2.296619792628992</x:v>
       </x:c>
       <x:c r="O9" t="n">
-        <x:v>2.296619792628992</x:v>
-      </x:c>
-      <x:c r="P9" t="n">
         <x:v>58.1968179959776</x:v>
       </x:c>
-      <x:c r="Q9" t="inlineStr">
+      <x:c r="P9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R9"/>
+      <x:c r="Q9"/>
+      <x:c r="R9" t="n">
+        <x:v>2.677496374479454</x:v>
+      </x:c>
       <x:c r="S9" t="n">
-        <x:v>2.677496374479454</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="T9" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="U9" t="n">
         <x:v>7.539453223948219</x:v>
       </x:c>
-      <x:c r="V9" t="b">
+      <x:c r="U9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V9" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X9" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
@@ -1108,68 +1112,66 @@
         </x:is>
       </x:c>
       <x:c r="D10" t="n">
-        <x:v>59</x:v>
+        <x:v>28.5269718170166</x:v>
       </x:c>
       <x:c r="E10" t="n">
-        <x:v>28.5269718170166</x:v>
+        <x:v>14.46787881851196</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>14.46787881851196</x:v>
+        <x:v>12.34323930740356</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>12.34323930740356</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H10" t="n">
-        <x:v>126</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I10" t="n">
-        <x:v>105</x:v>
+        <x:v>6.170740971647149</x:v>
       </x:c>
       <x:c r="J10" t="n">
-        <x:v>6.170740971647149</x:v>
+        <x:v>2.981756714242299</x:v>
       </x:c>
       <x:c r="K10" t="n">
-        <x:v>2.981756714242299</x:v>
+        <x:v>0.3353727670750336</x:v>
       </x:c>
       <x:c r="L10" t="n">
-        <x:v>0.3353727670750336</x:v>
+        <x:v>-3.722851287062513</x:v>
       </x:c>
       <x:c r="M10" t="n">
-        <x:v>-3.722851287062513</x:v>
+        <x:v>4.232358667613996</x:v>
       </x:c>
       <x:c r="N10" t="n">
-        <x:v>4.232358667613996</x:v>
+        <x:v>1.122446300770694</x:v>
       </x:c>
       <x:c r="O10" t="n">
-        <x:v>1.122446300770694</x:v>
-      </x:c>
-      <x:c r="P10" t="n">
         <x:v>56.06022395177172</x:v>
       </x:c>
-      <x:c r="Q10" t="inlineStr">
+      <x:c r="P10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R10"/>
+      <x:c r="Q10"/>
+      <x:c r="R10" t="n">
+        <x:v>2.919768138928236</x:v>
+      </x:c>
       <x:c r="S10" t="n">
-        <x:v>2.919768138928236</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="T10" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="U10" t="n">
         <x:v>5.320091989629738</x:v>
       </x:c>
-      <x:c r="V10" t="b">
+      <x:c r="U10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V10" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X10" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
@@ -1188,62 +1190,60 @@
         </x:is>
       </x:c>
       <x:c r="D11" t="n">
-        <x:v>35</x:v>
+        <x:v>27.77320384979248</x:v>
       </x:c>
       <x:c r="E11" t="n">
-        <x:v>27.77320384979248</x:v>
+        <x:v>15.78073024749756</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>15.78073024749756</x:v>
+        <x:v>13.79810762405396</x:v>
       </x:c>
       <x:c r="G11" t="n">
-        <x:v>13.79810762405396</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H11" t="n">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I11" t="n">
-        <x:v>44</x:v>
+        <x:v>4.362331529296503</x:v>
       </x:c>
       <x:c r="J11" t="n">
-        <x:v>4.362331529296503</x:v>
+        <x:v>2.265954929560903</x:v>
       </x:c>
       <x:c r="K11" t="n">
-        <x:v>2.265954929560903</x:v>
+        <x:v>0.4413150442466126</x:v>
       </x:c>
       <x:c r="L11" t="n">
-        <x:v>0.4413150442466126</x:v>
+        <x:v>-2.876810693797233</x:v>
       </x:c>
       <x:c r="M11" t="n">
-        <x:v>-2.876810693797233</x:v>
+        <x:v>4.254557946741915</x:v>
       </x:c>
       <x:c r="N11" t="n">
-        <x:v>4.254557946741915</x:v>
+        <x:v>1.672197952010383</x:v>
       </x:c>
       <x:c r="O11" t="n">
-        <x:v>1.672197952010383</x:v>
-      </x:c>
-      <x:c r="P11" t="n">
         <x:v>53.66374668339681</x:v>
       </x:c>
-      <x:c r="Q11" t="inlineStr">
+      <x:c r="P11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q11"/>
       <x:c r="R11"/>
       <x:c r="S11"/>
       <x:c r="T11"/>
-      <x:c r="U11"/>
-      <x:c r="V11" t="b">
-        <x:v>1</x:v>
+      <x:c r="U11" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V11" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="inlineStr">
@@ -1262,68 +1262,66 @@
         </x:is>
       </x:c>
       <x:c r="D12" t="n">
-        <x:v>60</x:v>
+        <x:v>30.44647789001465</x:v>
       </x:c>
       <x:c r="E12" t="n">
-        <x:v>30.44647789001465</x:v>
+        <x:v>15.21294164657593</x:v>
       </x:c>
       <x:c r="F12" t="n">
-        <x:v>15.21294164657593</x:v>
+        <x:v>12.60205602645874</x:v>
       </x:c>
       <x:c r="G12" t="n">
-        <x:v>12.60205602645874</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H12" t="n">
-        <x:v>96</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I12" t="n">
-        <x:v>82</x:v>
+        <x:v>3.826464928503511</x:v>
       </x:c>
       <x:c r="J12" t="n">
-        <x:v>3.826464928503511</x:v>
+        <x:v>2.785014426572873</x:v>
       </x:c>
       <x:c r="K12" t="n">
-        <x:v>2.785014426572873</x:v>
+        <x:v>0.3590645672994089</x:v>
       </x:c>
       <x:c r="L12" t="n">
-        <x:v>0.3590645672994089</x:v>
+        <x:v>2.768713053820193</x:v>
       </x:c>
       <x:c r="M12" t="n">
-        <x:v>2.768713053820193</x:v>
+        <x:v>-3.036268518604399</x:v>
       </x:c>
       <x:c r="N12" t="n">
-        <x:v>-3.036268518604399</x:v>
+        <x:v>0.7909576048849446</x:v>
       </x:c>
       <x:c r="O12" t="n">
-        <x:v>0.7909576048849446</x:v>
-      </x:c>
-      <x:c r="P12" t="n">
         <x:v>56.92613991711364</x:v>
       </x:c>
-      <x:c r="Q12" t="inlineStr">
+      <x:c r="P12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R12"/>
+      <x:c r="Q12"/>
+      <x:c r="R12" t="n">
+        <x:v>2.885612913727508</x:v>
+      </x:c>
       <x:c r="S12" t="n">
-        <x:v>2.885612913727508</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="T12" t="n">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="U12" t="n">
         <x:v>3.9864834585944</x:v>
       </x:c>
-      <x:c r="V12" t="b">
-        <x:v>1</x:v>
+      <x:c r="U12" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V12" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X12" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="inlineStr">
@@ -1342,72 +1340,70 @@
         </x:is>
       </x:c>
       <x:c r="D13" t="n">
-        <x:v>59</x:v>
+        <x:v>30.99716186523438</x:v>
       </x:c>
       <x:c r="E13" t="n">
-        <x:v>30.99716186523438</x:v>
+        <x:v>15.54600048065186</x:v>
       </x:c>
       <x:c r="F13" t="n">
-        <x:v>15.54600048065186</x:v>
+        <x:v>13.06305122375488</x:v>
       </x:c>
       <x:c r="G13" t="n">
-        <x:v>13.06305122375488</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H13" t="n">
-        <x:v>146</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I13" t="n">
-        <x:v>125</x:v>
+        <x:v>15.58409461579898</x:v>
       </x:c>
       <x:c r="J13" t="n">
-        <x:v>15.58409461579898</x:v>
+        <x:v>3.151846682224342</x:v>
       </x:c>
       <x:c r="K13" t="n">
-        <x:v>3.151846682224342</x:v>
+        <x:v>0.3172743159239819</x:v>
       </x:c>
       <x:c r="L13" t="n">
-        <x:v>0.3172743159239819</x:v>
+        <x:v>1.774807641043421</x:v>
       </x:c>
       <x:c r="M13" t="n">
-        <x:v>1.774807641043421</x:v>
+        <x:v>4.222401946168535</x:v>
       </x:c>
       <x:c r="N13" t="n">
-        <x:v>4.222401946168535</x:v>
+        <x:v>2.113620083874158</x:v>
       </x:c>
       <x:c r="O13" t="n">
-        <x:v>2.113620083874158</x:v>
-      </x:c>
-      <x:c r="P13" t="n">
         <x:v>57.12813048263644</x:v>
       </x:c>
+      <x:c r="P13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q13" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R13" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fit error above 10% of the radius</x:t>
         </x:is>
       </x:c>
+      <x:c r="R13" t="n">
+        <x:v>2.926180955525751</x:v>
+      </x:c>
       <x:c r="S13" t="n">
-        <x:v>2.926180955525751</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="T13" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="U13" t="n">
         <x:v>6.191524468502994</x:v>
       </x:c>
-      <x:c r="V13" t="b">
+      <x:c r="U13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V13" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X13" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="inlineStr">
@@ -1426,72 +1422,70 @@
         </x:is>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>30</x:v>
+        <x:v>30.58197402954102</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>30.58197402954102</x:v>
+        <x:v>14.8689751625061</x:v>
       </x:c>
       <x:c r="F14" t="n">
-        <x:v>14.8689751625061</x:v>
+        <x:v>16.57603168487549</x:v>
       </x:c>
       <x:c r="G14" t="n">
-        <x:v>16.57603168487549</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H14" t="n">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I14" t="n">
-        <x:v>36</x:v>
+        <x:v>8.564183314477688</x:v>
       </x:c>
       <x:c r="J14" t="n">
-        <x:v>8.564183314477688</x:v>
+        <x:v>2.425771216650445</x:v>
       </x:c>
       <x:c r="K14" t="n">
-        <x:v>2.425771216650445</x:v>
+        <x:v>0.4122400303606623</x:v>
       </x:c>
       <x:c r="L14" t="n">
-        <x:v>0.4122400303606623</x:v>
+        <x:v>4.8539291207604</x:v>
       </x:c>
       <x:c r="M14" t="n">
-        <x:v>4.8539291207604</x:v>
+        <x:v>1.308709797248347</x:v>
       </x:c>
       <x:c r="N14" t="n">
-        <x:v>1.308709797248347</x:v>
+        <x:v>1.811309822326365</x:v>
       </x:c>
       <x:c r="O14" t="n">
-        <x:v>1.811309822326365</x:v>
-      </x:c>
-      <x:c r="P14" t="n">
         <x:v>57.87585465510357</x:v>
       </x:c>
+      <x:c r="P14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q14" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R14" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fewer than 40 inliers</x:t>
         </x:is>
       </x:c>
+      <x:c r="R14" t="n">
+        <x:v>2.086790506043905</x:v>
+      </x:c>
       <x:c r="S14" t="n">
-        <x:v>2.086790506043905</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="T14" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="U14" t="n">
         <x:v>6.572487375342797</x:v>
       </x:c>
-      <x:c r="V14" t="b">
+      <x:c r="U14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V14" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X14" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="inlineStr">
@@ -1510,68 +1504,66 @@
         </x:is>
       </x:c>
       <x:c r="D15" t="n">
-        <x:v>50</x:v>
+        <x:v>32.83447742462158</x:v>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>32.83447742462158</x:v>
+        <x:v>14.99247026443481</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>14.99247026443481</x:v>
+        <x:v>13.21341896057129</x:v>
       </x:c>
       <x:c r="G15" t="n">
-        <x:v>13.21341896057129</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H15" t="n">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I15" t="n">
-        <x:v>89</x:v>
+        <x:v>6.993682110609015</x:v>
       </x:c>
       <x:c r="J15" t="n">
-        <x:v>6.993682110609015</x:v>
+        <x:v>2.629056270846436</x:v>
       </x:c>
       <x:c r="K15" t="n">
-        <x:v>2.629056270846436</x:v>
+        <x:v>0.3803646240245918</x:v>
       </x:c>
       <x:c r="L15" t="n">
-        <x:v>0.3803646240245918</x:v>
+        <x:v>-3.095690116529104</x:v>
       </x:c>
       <x:c r="M15" t="n">
-        <x:v>-3.095690116529104</x:v>
+        <x:v>4.414867915795669</x:v>
       </x:c>
       <x:c r="N15" t="n">
-        <x:v>4.414867915795669</x:v>
+        <x:v>0.899398960814792</x:v>
       </x:c>
       <x:c r="O15" t="n">
-        <x:v>0.899398960814792</x:v>
-      </x:c>
-      <x:c r="P15" t="n">
         <x:v>60.54125949567407</x:v>
       </x:c>
-      <x:c r="Q15" t="inlineStr">
+      <x:c r="P15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R15"/>
+      <x:c r="Q15"/>
+      <x:c r="R15" t="n">
+        <x:v>2.595454941668886</x:v>
+      </x:c>
       <x:c r="S15" t="n">
-        <x:v>2.595454941668886</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="T15" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="U15" t="n">
         <x:v>6.86217351858051</x:v>
       </x:c>
-      <x:c r="V15" t="b">
+      <x:c r="U15" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V15" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X15" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="inlineStr">
@@ -1590,68 +1582,66 @@
         </x:is>
       </x:c>
       <x:c r="D16" t="n">
-        <x:v>40</x:v>
+        <x:v>32.24104595184326</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>32.24104595184326</x:v>
+        <x:v>14.57285976409912</x:v>
       </x:c>
       <x:c r="F16" t="n">
-        <x:v>14.57285976409912</x:v>
+        <x:v>13.14558696746826</x:v>
       </x:c>
       <x:c r="G16" t="n">
-        <x:v>13.14558696746826</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H16" t="n">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I16" t="n">
-        <x:v>64</x:v>
+        <x:v>7.54038033310456</x:v>
       </x:c>
       <x:c r="J16" t="n">
-        <x:v>7.54038033310456</x:v>
+        <x:v>2.610057421289604</x:v>
       </x:c>
       <x:c r="K16" t="n">
-        <x:v>2.610057421289604</x:v>
+        <x:v>0.3831333333294674</x:v>
       </x:c>
       <x:c r="L16" t="n">
-        <x:v>0.3831333333294674</x:v>
+        <x:v>-2.90954429071874</x:v>
       </x:c>
       <x:c r="M16" t="n">
-        <x:v>-2.90954429071874</x:v>
+        <x:v>5.017458622594094</x:v>
       </x:c>
       <x:c r="N16" t="n">
-        <x:v>5.017458622594094</x:v>
+        <x:v>0.8798148019798796</x:v>
       </x:c>
       <x:c r="O16" t="n">
-        <x:v>0.8798148019798796</x:v>
-      </x:c>
-      <x:c r="P16" t="n">
         <x:v>59.7387759171306</x:v>
       </x:c>
-      <x:c r="Q16" t="inlineStr">
+      <x:c r="P16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R16"/>
+      <x:c r="Q16"/>
+      <x:c r="R16" t="n">
+        <x:v>2.3354911289575</x:v>
+      </x:c>
       <x:c r="S16" t="n">
-        <x:v>2.3354911289575</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="T16" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="U16" t="n">
         <x:v>7.178845826612005</x:v>
       </x:c>
-      <x:c r="V16" t="b">
+      <x:c r="U16" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V16" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X16" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="inlineStr">
@@ -1670,68 +1660,66 @@
         </x:is>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>59</x:v>
+        <x:v>33.41120910644531</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>33.41120910644531</x:v>
+        <x:v>14.68073606491089</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>14.68073606491089</x:v>
+        <x:v>12.42964315414429</x:v>
       </x:c>
       <x:c r="G17" t="n">
-        <x:v>12.42964315414429</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H17" t="n">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I17" t="n">
-        <x:v>76</x:v>
+        <x:v>6.486458942246635</x:v>
       </x:c>
       <x:c r="J17" t="n">
-        <x:v>6.486458942246635</x:v>
+        <x:v>2.868883951190564</x:v>
       </x:c>
       <x:c r="K17" t="n">
-        <x:v>2.868883951190564</x:v>
+        <x:v>0.3485676022499996</x:v>
       </x:c>
       <x:c r="L17" t="n">
-        <x:v>0.3485676022499996</x:v>
+        <x:v>3.891688727161067</x:v>
       </x:c>
       <x:c r="M17" t="n">
-        <x:v>3.891688727161067</x:v>
+        <x:v>4.505035092997445</x:v>
       </x:c>
       <x:c r="N17" t="n">
-        <x:v>4.505035092997445</x:v>
+        <x:v>1.049226800921698</x:v>
       </x:c>
       <x:c r="O17" t="n">
-        <x:v>1.049226800921698</x:v>
-      </x:c>
-      <x:c r="P17" t="n">
         <x:v>61.27740408219388</x:v>
       </x:c>
-      <x:c r="Q17" t="inlineStr">
+      <x:c r="P17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R17"/>
+      <x:c r="Q17"/>
+      <x:c r="R17" t="n">
+        <x:v>2.913289333621533</x:v>
+      </x:c>
       <x:c r="S17" t="n">
-        <x:v>2.913289333621533</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="T17" t="n">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="U17" t="n">
         <x:v>6.185117558736484</x:v>
       </x:c>
-      <x:c r="V17" t="b">
+      <x:c r="U17" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V17" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X17" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="inlineStr">
@@ -1750,72 +1738,70 @@
         </x:is>
       </x:c>
       <x:c r="D18" t="n">
-        <x:v>59</x:v>
+        <x:v>36.59878444671631</x:v>
       </x:c>
       <x:c r="E18" t="n">
-        <x:v>36.59878444671631</x:v>
+        <x:v>18.77428531646729</x:v>
       </x:c>
       <x:c r="F18" t="n">
-        <x:v>18.77428531646729</x:v>
+        <x:v>16.59297513961792</x:v>
       </x:c>
       <x:c r="G18" t="n">
-        <x:v>16.59297513961792</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H18" t="n">
-        <x:v>114</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="I18" t="n">
-        <x:v>104</x:v>
+        <x:v>10.97996645136645</x:v>
       </x:c>
       <x:c r="J18" t="n">
-        <x:v>10.97996645136645</x:v>
+        <x:v>3.805647836246683</x:v>
       </x:c>
       <x:c r="K18" t="n">
-        <x:v>3.805647836246683</x:v>
+        <x:v>0.2627673507978208</x:v>
       </x:c>
       <x:c r="L18" t="n">
-        <x:v>0.2627673507978208</x:v>
+        <x:v>-4.933573382725208</x:v>
       </x:c>
       <x:c r="M18" t="n">
-        <x:v>-4.933573382725208</x:v>
+        <x:v>5.931267098222903</x:v>
       </x:c>
       <x:c r="N18" t="n">
-        <x:v>5.931267098222903</x:v>
+        <x:v>0.5310665369061957</x:v>
       </x:c>
       <x:c r="O18" t="n">
-        <x:v>0.5310665369061957</x:v>
-      </x:c>
-      <x:c r="P18" t="n">
         <x:v>54.22527154793944</x:v>
       </x:c>
+      <x:c r="P18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R18" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fit error above 10% of the radius</x:t>
         </x:is>
       </x:c>
+      <x:c r="R18" t="n">
+        <x:v>4.195079215917118</x:v>
+      </x:c>
       <x:c r="S18" t="n">
-        <x:v>4.195079215917118</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="T18" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="U18" t="n">
         <x:v>8.26844659480396</x:v>
       </x:c>
-      <x:c r="V18" t="b">
-        <x:v>1</x:v>
+      <x:c r="U18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V18" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X18" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="inlineStr">
@@ -1834,68 +1820,66 @@
         </x:is>
       </x:c>
       <x:c r="D19" t="n">
-        <x:v>60</x:v>
+        <x:v>37.91449642181396</x:v>
       </x:c>
       <x:c r="E19" t="n">
-        <x:v>37.91449642181396</x:v>
+        <x:v>19.49320697784424</x:v>
       </x:c>
       <x:c r="F19" t="n">
-        <x:v>19.49320697784424</x:v>
+        <x:v>16.71068286895752</x:v>
       </x:c>
       <x:c r="G19" t="n">
-        <x:v>16.71068286895752</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H19" t="n">
-        <x:v>112</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I19" t="n">
-        <x:v>101</x:v>
+        <x:v>7.720437793678411</x:v>
       </x:c>
       <x:c r="J19" t="n">
-        <x:v>7.720437793678411</x:v>
+        <x:v>3.650198609208236</x:v>
       </x:c>
       <x:c r="K19" t="n">
-        <x:v>3.650198609208236</x:v>
+        <x:v>0.2739576957476595</x:v>
       </x:c>
       <x:c r="L19" t="n">
-        <x:v>0.2739576957476595</x:v>
+        <x:v>-4.526640480440077</x:v>
       </x:c>
       <x:c r="M19" t="n">
-        <x:v>-4.526640480440077</x:v>
+        <x:v>-3.931286130597048</x:v>
       </x:c>
       <x:c r="N19" t="n">
-        <x:v>-3.931286130597048</x:v>
+        <x:v>0.4308785760586806</x:v>
       </x:c>
       <x:c r="O19" t="n">
-        <x:v>0.4308785760586806</x:v>
-      </x:c>
-      <x:c r="P19" t="n">
         <x:v>55.83477324996443</x:v>
       </x:c>
-      <x:c r="Q19" t="inlineStr">
+      <x:c r="P19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R19"/>
+      <x:c r="Q19"/>
+      <x:c r="R19" t="n">
+        <x:v>3.930205763740083</x:v>
+      </x:c>
       <x:c r="S19" t="n">
-        <x:v>3.930205763740083</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="T19" t="n">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="U19" t="n">
         <x:v>7.756603090354481</x:v>
       </x:c>
-      <x:c r="V19" t="b">
-        <x:v>1</x:v>
+      <x:c r="U19" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V19" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W19" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X19" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="X19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="inlineStr">
@@ -1914,62 +1898,60 @@
         </x:is>
       </x:c>
       <x:c r="D20" t="n">
-        <x:v>50</x:v>
+        <x:v>31.37033462524414</x:v>
       </x:c>
       <x:c r="E20" t="n">
-        <x:v>31.37033462524414</x:v>
+        <x:v>17.68332242965698</x:v>
       </x:c>
       <x:c r="F20" t="n">
-        <x:v>17.68332242965698</x:v>
+        <x:v>18.74435997009277</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>18.74435997009277</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H20" t="n">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I20" t="n">
-        <x:v>40</x:v>
+        <x:v>4.843620684248554</x:v>
       </x:c>
       <x:c r="J20" t="n">
-        <x:v>4.843620684248554</x:v>
+        <x:v>5.645421659177877</x:v>
       </x:c>
       <x:c r="K20" t="n">
-        <x:v>5.645421659177877</x:v>
+        <x:v>0.1771346872512667</x:v>
       </x:c>
       <x:c r="L20" t="n">
-        <x:v>0.1771346872512667</x:v>
+        <x:v>-4.514165415388122</x:v>
       </x:c>
       <x:c r="M20" t="n">
-        <x:v>-4.514165415388122</x:v>
+        <x:v>-7.462207040880179</x:v>
       </x:c>
       <x:c r="N20" t="n">
-        <x:v>-7.462207040880179</x:v>
+        <x:v>3.085823073365579</x:v>
       </x:c>
       <x:c r="O20" t="n">
-        <x:v>3.085823073365579</x:v>
-      </x:c>
-      <x:c r="P20" t="n">
         <x:v>46.57921396853177</x:v>
       </x:c>
-      <x:c r="Q20" t="inlineStr">
+      <x:c r="P20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q20"/>
       <x:c r="R20"/>
       <x:c r="S20"/>
       <x:c r="T20"/>
-      <x:c r="U20"/>
-      <x:c r="V20" t="b">
+      <x:c r="U20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V20" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X20" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="inlineStr">
@@ -1988,68 +1970,66 @@
         </x:is>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>60</x:v>
+        <x:v>23.34909152984619</x:v>
       </x:c>
       <x:c r="E21" t="n">
-        <x:v>23.34909152984619</x:v>
+        <x:v>15.02893733978271</x:v>
       </x:c>
       <x:c r="F21" t="n">
-        <x:v>15.02893733978271</x:v>
+        <x:v>12.65357875823975</x:v>
       </x:c>
       <x:c r="G21" t="n">
-        <x:v>12.65357875823975</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H21" t="n">
-        <x:v>75</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I21" t="n">
-        <x:v>66</x:v>
+        <x:v>7.565587945742087</x:v>
       </x:c>
       <x:c r="J21" t="n">
-        <x:v>7.565587945742087</x:v>
+        <x:v>2.864592367297842</x:v>
       </x:c>
       <x:c r="K21" t="n">
-        <x:v>2.864592367297842</x:v>
+        <x:v>0.3490898081751491</x:v>
       </x:c>
       <x:c r="L21" t="n">
-        <x:v>0.3490898081751491</x:v>
+        <x:v>1.377743714874796</x:v>
       </x:c>
       <x:c r="M21" t="n">
-        <x:v>1.377743714874796</x:v>
+        <x:v>4.506057672894588</x:v>
       </x:c>
       <x:c r="N21" t="n">
-        <x:v>4.506057672894588</x:v>
+        <x:v>1.211189903737082</x:v>
       </x:c>
       <x:c r="O21" t="n">
-        <x:v>1.211189903737082</x:v>
-      </x:c>
-      <x:c r="P21" t="n">
         <x:v>53.45800850910134</x:v>
       </x:c>
-      <x:c r="Q21" t="inlineStr">
+      <x:c r="P21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R21"/>
+      <x:c r="Q21"/>
+      <x:c r="R21" t="n">
+        <x:v>5.625530646040959</x:v>
+      </x:c>
       <x:c r="S21" t="n">
-        <x:v>5.625530646040959</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="T21" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="U21" t="n">
         <x:v>3.053814040173407</x:v>
       </x:c>
-      <x:c r="V21" t="b">
+      <x:c r="U21" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V21" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X21" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="inlineStr">
@@ -2068,62 +2048,60 @@
         </x:is>
       </x:c>
       <x:c r="D22" t="n">
-        <x:v>60</x:v>
+        <x:v>24.51808643341064</x:v>
       </x:c>
       <x:c r="E22" t="n">
-        <x:v>24.51808643341064</x:v>
+        <x:v>14.96967935562134</x:v>
       </x:c>
       <x:c r="F22" t="n">
-        <x:v>14.96967935562134</x:v>
+        <x:v>12.42033100128174</x:v>
       </x:c>
       <x:c r="G22" t="n">
-        <x:v>12.42033100128174</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H22" t="n">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I22" t="n">
-        <x:v>73</x:v>
+        <x:v>8.550606724210903</x:v>
       </x:c>
       <x:c r="J22" t="n">
-        <x:v>8.550606724210903</x:v>
+        <x:v>2.868042660270933</x:v>
       </x:c>
       <x:c r="K22" t="n">
-        <x:v>2.868042660270933</x:v>
+        <x:v>0.3486698485529269</x:v>
       </x:c>
       <x:c r="L22" t="n">
-        <x:v>0.3486698485529269</x:v>
+        <x:v>-4.060267608623356</x:v>
       </x:c>
       <x:c r="M22" t="n">
-        <x:v>-4.060267608623356</x:v>
+        <x:v>4.647112947204072</x:v>
       </x:c>
       <x:c r="N22" t="n">
-        <x:v>4.647112947204072</x:v>
+        <x:v>0.5886750014657761</x:v>
       </x:c>
       <x:c r="O22" t="n">
-        <x:v>0.5886750014657761</x:v>
-      </x:c>
-      <x:c r="P22" t="n">
         <x:v>48.18048828443027</x:v>
       </x:c>
-      <x:c r="Q22" t="inlineStr">
+      <x:c r="P22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q22"/>
       <x:c r="R22"/>
       <x:c r="S22"/>
       <x:c r="T22"/>
-      <x:c r="U22"/>
-      <x:c r="V22" t="b">
+      <x:c r="U22" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X22" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="inlineStr">
@@ -2142,68 +2120,66 @@
         </x:is>
       </x:c>
       <x:c r="D23" t="n">
-        <x:v>40</x:v>
+        <x:v>26.75342655181885</x:v>
       </x:c>
       <x:c r="E23" t="n">
-        <x:v>26.75342655181885</x:v>
+        <x:v>15.26019096374512</x:v>
       </x:c>
       <x:c r="F23" t="n">
-        <x:v>15.26019096374512</x:v>
+        <x:v>12.65590858459473</x:v>
       </x:c>
       <x:c r="G23" t="n">
-        <x:v>12.65590858459473</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H23" t="n">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I23" t="n">
-        <x:v>49</x:v>
+        <x:v>5.152419189828262</x:v>
       </x:c>
       <x:c r="J23" t="n">
-        <x:v>5.152419189828262</x:v>
+        <x:v>2.837380513195833</x:v>
       </x:c>
       <x:c r="K23" t="n">
-        <x:v>2.837380513195833</x:v>
+        <x:v>0.3524377486027307</x:v>
       </x:c>
       <x:c r="L23" t="n">
-        <x:v>0.3524377486027307</x:v>
+        <x:v>-3.186751086940118</x:v>
       </x:c>
       <x:c r="M23" t="n">
-        <x:v>-3.186751086940118</x:v>
+        <x:v>-3.205618969681091</x:v>
       </x:c>
       <x:c r="N23" t="n">
-        <x:v>-3.205618969681091</x:v>
+        <x:v>0.09293979467059464</x:v>
       </x:c>
       <x:c r="O23" t="n">
-        <x:v>0.09293979467059464</x:v>
-      </x:c>
-      <x:c r="P23" t="n">
         <x:v>50.13876872659961</x:v>
       </x:c>
-      <x:c r="Q23" t="inlineStr">
+      <x:c r="P23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R23"/>
+      <x:c r="Q23"/>
+      <x:c r="R23" t="n">
+        <x:v>3.099724909999179</x:v>
+      </x:c>
       <x:c r="S23" t="n">
-        <x:v>3.099724909999179</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="T23" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="U23" t="n">
         <x:v>21.8903332859391</x:v>
       </x:c>
-      <x:c r="V23" t="b">
+      <x:c r="U23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X23" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="inlineStr">
@@ -2222,62 +2198,60 @@
         </x:is>
       </x:c>
       <x:c r="D24" t="n">
-        <x:v>40</x:v>
+        <x:v>29.11089992523193</x:v>
       </x:c>
       <x:c r="E24" t="n">
-        <x:v>29.11089992523193</x:v>
+        <x:v>16.56497764587402</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>16.56497764587402</x:v>
+        <x:v>13.61943912506104</x:v>
       </x:c>
       <x:c r="G24" t="n">
-        <x:v>13.61943912506104</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H24" t="n">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I24" t="n">
-        <x:v>43</x:v>
+        <x:v>5.465705350107406</x:v>
       </x:c>
       <x:c r="J24" t="n">
-        <x:v>5.465705350107406</x:v>
+        <x:v>2.184943692970263</x:v>
       </x:c>
       <x:c r="K24" t="n">
-        <x:v>2.184943692970263</x:v>
+        <x:v>0.4576776981564119</x:v>
       </x:c>
       <x:c r="L24" t="n">
-        <x:v>0.4576776981564119</x:v>
+        <x:v>-3.990004181549857</x:v>
       </x:c>
       <x:c r="M24" t="n">
-        <x:v>-3.990004181549857</x:v>
+        <x:v>-2.371223702146507</x:v>
       </x:c>
       <x:c r="N24" t="n">
-        <x:v>-2.371223702146507</x:v>
+        <x:v>1.050246441118778</x:v>
       </x:c>
       <x:c r="O24" t="n">
-        <x:v>1.050246441118778</x:v>
-      </x:c>
-      <x:c r="P24" t="n">
         <x:v>52.96017081651942</x:v>
       </x:c>
-      <x:c r="Q24" t="inlineStr">
+      <x:c r="P24" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q24"/>
       <x:c r="R24"/>
       <x:c r="S24"/>
       <x:c r="T24"/>
-      <x:c r="U24"/>
-      <x:c r="V24" t="b">
+      <x:c r="U24" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V24" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X24" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="inlineStr">
@@ -2296,68 +2270,66 @@
         </x:is>
       </x:c>
       <x:c r="D25" t="n">
-        <x:v>59</x:v>
+        <x:v>26.37747573852539</x:v>
       </x:c>
       <x:c r="E25" t="n">
-        <x:v>26.37747573852539</x:v>
+        <x:v>14.21726703643799</x:v>
       </x:c>
       <x:c r="F25" t="n">
-        <x:v>14.21726703643799</x:v>
+        <x:v>11.94507598876953</x:v>
       </x:c>
       <x:c r="G25" t="n">
-        <x:v>11.94507598876953</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H25" t="n">
-        <x:v>104</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I25" t="n">
-        <x:v>95</x:v>
+        <x:v>4.785510943284861</x:v>
       </x:c>
       <x:c r="J25" t="n">
-        <x:v>4.785510943284861</x:v>
+        <x:v>2.926106427650632</x:v>
       </x:c>
       <x:c r="K25" t="n">
-        <x:v>2.926106427650632</x:v>
+        <x:v>0.3417510691170926</x:v>
       </x:c>
       <x:c r="L25" t="n">
-        <x:v>0.3417510691170926</x:v>
+        <x:v>-3.998471860910001</x:v>
       </x:c>
       <x:c r="M25" t="n">
-        <x:v>-3.998471860910001</x:v>
+        <x:v>4.075857756116824</x:v>
       </x:c>
       <x:c r="N25" t="n">
-        <x:v>4.075857756116824</x:v>
+        <x:v>0.3721515604173745</x:v>
       </x:c>
       <x:c r="O25" t="n">
-        <x:v>0.3721515604173745</x:v>
-      </x:c>
-      <x:c r="P25" t="n">
         <x:v>53.41632601534975</x:v>
       </x:c>
-      <x:c r="Q25" t="inlineStr">
+      <x:c r="P25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R25"/>
+      <x:c r="Q25"/>
+      <x:c r="R25" t="n">
+        <x:v>2.767601857390287</x:v>
+      </x:c>
       <x:c r="S25" t="n">
-        <x:v>2.767601857390287</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="T25" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="U25" t="n">
         <x:v>5.804016019860674</x:v>
       </x:c>
-      <x:c r="V25" t="b">
+      <x:c r="U25" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X25" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="inlineStr">
@@ -2376,68 +2348,66 @@
         </x:is>
       </x:c>
       <x:c r="D26" t="n">
+        <x:v>27.04212284088135</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>14.11539268493652</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>12.00770616531372</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H26" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E26" t="n">
-        <x:v>27.04212284088135</x:v>
-      </x:c>
-      <x:c r="F26" t="n">
-        <x:v>14.11539268493652</x:v>
-      </x:c>
-      <x:c r="G26" t="n">
-        <x:v>12.00770616531372</x:v>
-      </x:c>
-      <x:c r="H26" t="n">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="I26" t="n">
-        <x:v>40</x:v>
+        <x:v>3.908886531719385</x:v>
       </x:c>
       <x:c r="J26" t="n">
-        <x:v>3.908886531719385</x:v>
+        <x:v>2.177656970777421</x:v>
       </x:c>
       <x:c r="K26" t="n">
-        <x:v>2.177656970777421</x:v>
+        <x:v>0.4592091469957278</x:v>
       </x:c>
       <x:c r="L26" t="n">
-        <x:v>0.4592091469957278</x:v>
+        <x:v>1.436659667413868</x:v>
       </x:c>
       <x:c r="M26" t="n">
-        <x:v>1.436659667413868</x:v>
+        <x:v>-2.614290991124658</x:v>
       </x:c>
       <x:c r="N26" t="n">
-        <x:v>-2.614290991124658</x:v>
+        <x:v>0.1226579430193346</x:v>
       </x:c>
       <x:c r="O26" t="n">
-        <x:v>0.1226579430193346</x:v>
-      </x:c>
-      <x:c r="P26" t="n">
         <x:v>54.87551117962461</x:v>
       </x:c>
-      <x:c r="Q26" t="inlineStr">
+      <x:c r="P26" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R26"/>
+      <x:c r="Q26"/>
+      <x:c r="R26" t="n">
+        <x:v>2.2382405895586</x:v>
+      </x:c>
       <x:c r="S26" t="n">
-        <x:v>2.2382405895586</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="T26" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="U26" t="n">
         <x:v>3.711012685677085</x:v>
       </x:c>
-      <x:c r="V26" t="b">
-        <x:v>1</x:v>
+      <x:c r="U26" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V26" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W26" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X26" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="inlineStr">
@@ -2456,68 +2426,66 @@
         </x:is>
       </x:c>
       <x:c r="D27" t="n">
-        <x:v>40</x:v>
+        <x:v>26.69794082641602</x:v>
       </x:c>
       <x:c r="E27" t="n">
-        <x:v>26.69794082641602</x:v>
+        <x:v>15.10376405715942</x:v>
       </x:c>
       <x:c r="F27" t="n">
-        <x:v>15.10376405715942</x:v>
+        <x:v>12.42740345001221</x:v>
       </x:c>
       <x:c r="G27" t="n">
-        <x:v>12.42740345001221</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H27" t="n">
-        <x:v>98</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I27" t="n">
-        <x:v>85</x:v>
+        <x:v>6.340795831744384</x:v>
       </x:c>
       <x:c r="J27" t="n">
-        <x:v>6.340795831744384</x:v>
+        <x:v>2.587815743086492</x:v>
       </x:c>
       <x:c r="K27" t="n">
-        <x:v>2.587815743086492</x:v>
+        <x:v>0.3864262757777717</x:v>
       </x:c>
       <x:c r="L27" t="n">
-        <x:v>0.3864262757777717</x:v>
+        <x:v>-3.440390945591658</x:v>
       </x:c>
       <x:c r="M27" t="n">
-        <x:v>-3.440390945591658</x:v>
+        <x:v>-2.842637997086626</x:v>
       </x:c>
       <x:c r="N27" t="n">
-        <x:v>-2.842637997086626</x:v>
+        <x:v>0.595516229968642</x:v>
       </x:c>
       <x:c r="O27" t="n">
-        <x:v>0.595516229968642</x:v>
-      </x:c>
-      <x:c r="P27" t="n">
         <x:v>53.88706419200153</x:v>
       </x:c>
-      <x:c r="Q27" t="inlineStr">
+      <x:c r="P27" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R27"/>
+      <x:c r="Q27"/>
+      <x:c r="R27" t="n">
+        <x:v>2.703552858593691</x:v>
+      </x:c>
       <x:c r="S27" t="n">
-        <x:v>2.703552858593691</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="T27" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="U27" t="n">
         <x:v>7.011145591690154</x:v>
       </x:c>
-      <x:c r="V27" t="b">
-        <x:v>1</x:v>
+      <x:c r="U27" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V27" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X27" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="inlineStr">
@@ -2536,68 +2504,66 @@
         </x:is>
       </x:c>
       <x:c r="D28" t="n">
-        <x:v>60</x:v>
+        <x:v>30.21558284759521</x:v>
       </x:c>
       <x:c r="E28" t="n">
-        <x:v>30.21558284759521</x:v>
+        <x:v>16.59644460678101</x:v>
       </x:c>
       <x:c r="F28" t="n">
-        <x:v>16.59644460678101</x:v>
+        <x:v>16.25317525863647</x:v>
       </x:c>
       <x:c r="G28" t="n">
-        <x:v>16.25317525863647</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H28" t="n">
-        <x:v>92</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I28" t="n">
-        <x:v>84</x:v>
+        <x:v>3.757430318150741</x:v>
       </x:c>
       <x:c r="J28" t="n">
-        <x:v>3.757430318150741</x:v>
+        <x:v>3.709518976495147</x:v>
       </x:c>
       <x:c r="K28" t="n">
-        <x:v>3.709518976495147</x:v>
+        <x:v>0.2695767311978619</x:v>
       </x:c>
       <x:c r="L28" t="n">
-        <x:v>0.2695767311978619</x:v>
+        <x:v>-1.99594107327985</x:v>
       </x:c>
       <x:c r="M28" t="n">
-        <x:v>-1.99594107327985</x:v>
+        <x:v>-3.501552858946259</x:v>
       </x:c>
       <x:c r="N28" t="n">
-        <x:v>-3.501552858946259</x:v>
+        <x:v>2.007705380600264</x:v>
       </x:c>
       <x:c r="O28" t="n">
-        <x:v>2.007705380600264</x:v>
-      </x:c>
-      <x:c r="P28" t="n">
         <x:v>54.82308631065671</x:v>
       </x:c>
-      <x:c r="Q28" t="inlineStr">
+      <x:c r="P28" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R28"/>
+      <x:c r="Q28"/>
+      <x:c r="R28" t="n">
+        <x:v>3.737542368231857</x:v>
+      </x:c>
       <x:c r="S28" t="n">
-        <x:v>3.737542368231857</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="T28" t="n">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="U28" t="n">
         <x:v>3.197943540114028</x:v>
       </x:c>
-      <x:c r="V28" t="b">
+      <x:c r="U28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V28" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X28" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="inlineStr">
@@ -2616,72 +2582,70 @@
         </x:is>
       </x:c>
       <x:c r="D29" t="n">
-        <x:v>50</x:v>
+        <x:v>33.25169086456299</x:v>
       </x:c>
       <x:c r="E29" t="n">
-        <x:v>33.25169086456299</x:v>
+        <x:v>18.2786865234375</x:v>
       </x:c>
       <x:c r="F29" t="n">
-        <x:v>18.2786865234375</x:v>
+        <x:v>16.88223648071289</x:v>
       </x:c>
       <x:c r="G29" t="n">
-        <x:v>16.88223648071289</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H29" t="n">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I29" t="n">
-        <x:v>26</x:v>
+        <x:v>7.55912379597455</x:v>
       </x:c>
       <x:c r="J29" t="n">
-        <x:v>7.55912379597455</x:v>
+        <x:v>2.263033419996254</x:v>
       </x:c>
       <x:c r="K29" t="n">
-        <x:v>2.263033419996254</x:v>
+        <x:v>0.4418847689848324</x:v>
       </x:c>
       <x:c r="L29" t="n">
-        <x:v>0.4418847689848324</x:v>
+        <x:v>-1.619843179823561</x:v>
       </x:c>
       <x:c r="M29" t="n">
-        <x:v>-1.619843179823561</x:v>
+        <x:v>3.805420730146433</x:v>
       </x:c>
       <x:c r="N29" t="n">
-        <x:v>3.805420730146433</x:v>
+        <x:v>1.72143866846209</x:v>
       </x:c>
       <x:c r="O29" t="n">
-        <x:v>1.72143866846209</x:v>
-      </x:c>
-      <x:c r="P29" t="n">
         <x:v>55.38152079047214</x:v>
       </x:c>
+      <x:c r="P29" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q29" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R29" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fewer than 40 inliers</x:t>
         </x:is>
       </x:c>
+      <x:c r="R29" t="n">
+        <x:v>5.094972346574971</x:v>
+      </x:c>
       <x:c r="S29" t="n">
-        <x:v>5.094972346574971</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="T29" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="U29" t="n">
         <x:v>1.575157675347321</x:v>
       </x:c>
-      <x:c r="V29" t="b">
+      <x:c r="U29" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V29" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X29" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="inlineStr">
@@ -2700,72 +2664,70 @@
         </x:is>
       </x:c>
       <x:c r="D30" t="n">
-        <x:v>59</x:v>
+        <x:v>28.58596420288086</x:v>
       </x:c>
       <x:c r="E30" t="n">
-        <x:v>28.58596420288086</x:v>
+        <x:v>16.24788904190063</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>16.24788904190063</x:v>
+        <x:v>13.37396478652954</x:v>
       </x:c>
       <x:c r="G30" t="n">
-        <x:v>13.37396478652954</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H30" t="n">
-        <x:v>109</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I30" t="n">
-        <x:v>95</x:v>
+        <x:v>10.33062429309862</x:v>
       </x:c>
       <x:c r="J30" t="n">
-        <x:v>10.33062429309862</x:v>
+        <x:v>3.842641354516009</x:v>
       </x:c>
       <x:c r="K30" t="n">
-        <x:v>3.842641354516009</x:v>
+        <x:v>0.2602376614785463</x:v>
       </x:c>
       <x:c r="L30" t="n">
-        <x:v>0.2602376614785463</x:v>
+        <x:v>-4.010251461761237</x:v>
       </x:c>
       <x:c r="M30" t="n">
-        <x:v>-4.010251461761237</x:v>
+        <x:v>-4.421962808759381</x:v>
       </x:c>
       <x:c r="N30" t="n">
-        <x:v>-4.421962808759381</x:v>
+        <x:v>0.6707079038729452</x:v>
       </x:c>
       <x:c r="O30" t="n">
-        <x:v>0.6707079038729452</x:v>
-      </x:c>
-      <x:c r="P30" t="n">
         <x:v>50.94312177045174</x:v>
       </x:c>
+      <x:c r="P30" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q30" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R30" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fit error above 10% of the radius</x:t>
         </x:is>
       </x:c>
+      <x:c r="R30" t="n">
+        <x:v>2.810634831172103</x:v>
+      </x:c>
       <x:c r="S30" t="n">
-        <x:v>2.810634831172103</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="T30" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="U30" t="n">
         <x:v>3.908183816157132</x:v>
       </x:c>
-      <x:c r="V30" t="b">
-        <x:v>1</x:v>
+      <x:c r="U30" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V30" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X30" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="inlineStr">
@@ -2784,68 +2746,66 @@
         </x:is>
       </x:c>
       <x:c r="D31" t="n">
-        <x:v>30</x:v>
+        <x:v>28.46683979034424</x:v>
       </x:c>
       <x:c r="E31" t="n">
-        <x:v>28.46683979034424</x:v>
+        <x:v>15.95134115219116</x:v>
       </x:c>
       <x:c r="F31" t="n">
-        <x:v>15.95134115219116</x:v>
+        <x:v>13.71569108963013</x:v>
       </x:c>
       <x:c r="G31" t="n">
-        <x:v>13.71569108963013</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H31" t="n">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:v>52</x:v>
+        <x:v>9.338272281058241</x:v>
       </x:c>
       <x:c r="J31" t="n">
-        <x:v>9.338272281058241</x:v>
+        <x:v>3.386447173698062</x:v>
       </x:c>
       <x:c r="K31" t="n">
-        <x:v>3.386447173698062</x:v>
+        <x:v>0.2952947288730277</x:v>
       </x:c>
       <x:c r="L31" t="n">
-        <x:v>0.2952947288730277</x:v>
+        <x:v>-3.535305752686731</x:v>
       </x:c>
       <x:c r="M31" t="n">
-        <x:v>-3.535305752686731</x:v>
+        <x:v>6.209864715190883</x:v>
       </x:c>
       <x:c r="N31" t="n">
-        <x:v>6.209864715190883</x:v>
+        <x:v>1.04775751223362</x:v>
       </x:c>
       <x:c r="O31" t="n">
-        <x:v>1.04775751223362</x:v>
-      </x:c>
-      <x:c r="P31" t="n">
         <x:v>51.22011747567101</x:v>
       </x:c>
-      <x:c r="Q31" t="inlineStr">
+      <x:c r="P31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R31"/>
+      <x:c r="Q31"/>
+      <x:c r="R31" t="n">
+        <x:v>3.590840096010553</x:v>
+      </x:c>
       <x:c r="S31" t="n">
-        <x:v>3.590840096010553</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="T31" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="U31" t="n">
         <x:v>8.328213834275761</x:v>
       </x:c>
-      <x:c r="V31" t="b">
+      <x:c r="U31" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V31" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X31" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="inlineStr">
@@ -2864,72 +2824,70 @@
         </x:is>
       </x:c>
       <x:c r="D32" t="n">
-        <x:v>55</x:v>
+        <x:v>28.56795310974121</x:v>
       </x:c>
       <x:c r="E32" t="n">
-        <x:v>28.56795310974121</x:v>
+        <x:v>15.56393432617188</x:v>
       </x:c>
       <x:c r="F32" t="n">
-        <x:v>15.56393432617188</x:v>
+        <x:v>13.27318143844604</x:v>
       </x:c>
       <x:c r="G32" t="n">
-        <x:v>13.27318143844604</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H32" t="n">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:v>36</x:v>
+        <x:v>7.916223622235143</x:v>
       </x:c>
       <x:c r="J32" t="n">
-        <x:v>7.916223622235143</x:v>
+        <x:v>3.84745612369259</x:v>
       </x:c>
       <x:c r="K32" t="n">
-        <x:v>3.84745612369259</x:v>
+        <x:v>0.2599119958359009</x:v>
       </x:c>
       <x:c r="L32" t="n">
-        <x:v>0.2599119958359009</x:v>
+        <x:v>-5.18335728051377</x:v>
       </x:c>
       <x:c r="M32" t="n">
-        <x:v>-5.18335728051377</x:v>
+        <x:v>5.72327399517627</x:v>
       </x:c>
       <x:c r="N32" t="n">
-        <x:v>5.72327399517627</x:v>
+        <x:v>1.041611224598838</x:v>
       </x:c>
       <x:c r="O32" t="n">
-        <x:v>1.041611224598838</x:v>
-      </x:c>
-      <x:c r="P32" t="n">
         <x:v>50.19415007652306</x:v>
       </x:c>
+      <x:c r="P32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q32" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R32" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fewer than 40 inliers</x:t>
         </x:is>
       </x:c>
+      <x:c r="R32" t="n">
+        <x:v>4.25559606214375</x:v>
+      </x:c>
       <x:c r="S32" t="n">
-        <x:v>4.25559606214375</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="T32" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="U32" t="n">
         <x:v>2.804441953304251</x:v>
       </x:c>
-      <x:c r="V32" t="b">
+      <x:c r="U32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V32" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X32" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="inlineStr">
@@ -2948,68 +2906,66 @@
         </x:is>
       </x:c>
       <x:c r="D33" t="n">
-        <x:v>59</x:v>
+        <x:v>29.57288551330566</x:v>
       </x:c>
       <x:c r="E33" t="n">
-        <x:v>29.57288551330566</x:v>
+        <x:v>17.39828968048096</x:v>
       </x:c>
       <x:c r="F33" t="n">
-        <x:v>17.39828968048096</x:v>
+        <x:v>17.12867832183838</x:v>
       </x:c>
       <x:c r="G33" t="n">
-        <x:v>17.12867832183838</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H33" t="n">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:v>63</x:v>
+        <x:v>6.20149964148462</x:v>
       </x:c>
       <x:c r="J33" t="n">
-        <x:v>6.20149964148462</x:v>
+        <x:v>3.123177342181059</x:v>
       </x:c>
       <x:c r="K33" t="n">
-        <x:v>3.123177342181059</x:v>
+        <x:v>0.3201867490821555</x:v>
       </x:c>
       <x:c r="L33" t="n">
-        <x:v>0.3201867490821555</x:v>
+        <x:v>-1.329567526885749</x:v>
       </x:c>
       <x:c r="M33" t="n">
-        <x:v>-1.329567526885749</x:v>
+        <x:v>4.353029250826304</x:v>
       </x:c>
       <x:c r="N33" t="n">
-        <x:v>4.353029250826304</x:v>
+        <x:v>0.8053987398694196</x:v>
       </x:c>
       <x:c r="O33" t="n">
-        <x:v>0.8053987398694196</x:v>
-      </x:c>
-      <x:c r="P33" t="n">
         <x:v>54.72715870039305</x:v>
       </x:c>
-      <x:c r="Q33" t="inlineStr">
+      <x:c r="P33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R33"/>
+      <x:c r="Q33"/>
+      <x:c r="R33" t="n">
+        <x:v>3.173347651396167</x:v>
+      </x:c>
       <x:c r="S33" t="n">
-        <x:v>3.173347651396167</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="T33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="U33" t="n">
         <x:v>3.637582165664634</x:v>
       </x:c>
-      <x:c r="V33" t="b">
+      <x:c r="U33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V33" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X33" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="inlineStr">
@@ -3028,68 +2984,66 @@
         </x:is>
       </x:c>
       <x:c r="D34" t="n">
-        <x:v>61</x:v>
+        <x:v>37.98007869720459</x:v>
       </x:c>
       <x:c r="E34" t="n">
-        <x:v>37.98007869720459</x:v>
+        <x:v>16.99123477935791</x:v>
       </x:c>
       <x:c r="F34" t="n">
-        <x:v>16.99123477935791</x:v>
+        <x:v>14.83643579483032</x:v>
       </x:c>
       <x:c r="G34" t="n">
-        <x:v>14.83643579483032</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H34" t="n">
-        <x:v>89</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:v>78</x:v>
+        <x:v>5.500360806805076</x:v>
       </x:c>
       <x:c r="J34" t="n">
-        <x:v>5.500360806805076</x:v>
+        <x:v>3.189232432358797</x:v>
       </x:c>
       <x:c r="K34" t="n">
-        <x:v>3.189232432358797</x:v>
+        <x:v>0.3135550704469624</x:v>
       </x:c>
       <x:c r="L34" t="n">
-        <x:v>0.3135550704469624</x:v>
+        <x:v>-2.657952877102554</x:v>
       </x:c>
       <x:c r="M34" t="n">
-        <x:v>-2.657952877102554</x:v>
+        <x:v>4.785386512807958</x:v>
       </x:c>
       <x:c r="N34" t="n">
-        <x:v>4.785386512807958</x:v>
+        <x:v>1.686108696136781</x:v>
       </x:c>
       <x:c r="O34" t="n">
-        <x:v>1.686108696136781</x:v>
-      </x:c>
-      <x:c r="P34" t="n">
         <x:v>62.44363848933006</x:v>
       </x:c>
-      <x:c r="Q34" t="inlineStr">
+      <x:c r="P34" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R34"/>
+      <x:c r="Q34"/>
+      <x:c r="R34" t="n">
+        <x:v>3.378179118419382</x:v>
+      </x:c>
       <x:c r="S34" t="n">
-        <x:v>3.378179118419382</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="T34" t="n">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="U34" t="n">
         <x:v>6.671247419234438</x:v>
       </x:c>
-      <x:c r="V34" t="b">
+      <x:c r="U34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V34" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W34" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X34" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="X34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="inlineStr">
@@ -3108,66 +3062,64 @@
         </x:is>
       </x:c>
       <x:c r="D35" t="n">
-        <x:v>50</x:v>
+        <x:v>33.23452663421631</x:v>
       </x:c>
       <x:c r="E35" t="n">
-        <x:v>33.23452663421631</x:v>
+        <x:v>18.97551441192627</x:v>
       </x:c>
       <x:c r="F35" t="n">
-        <x:v>18.97551441192627</x:v>
+        <x:v>16.67350149154663</x:v>
       </x:c>
       <x:c r="G35" t="n">
-        <x:v>16.67350149154663</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H35" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:v>75</x:v>
+        <x:v>10.31100850019581</x:v>
       </x:c>
       <x:c r="J35" t="n">
-        <x:v>10.31100850019581</x:v>
+        <x:v>3.565513100321019</x:v>
       </x:c>
       <x:c r="K35" t="n">
-        <x:v>3.565513100321019</x:v>
+        <x:v>0.2804645423711851</x:v>
       </x:c>
       <x:c r="L35" t="n">
-        <x:v>0.2804645423711851</x:v>
+        <x:v>-2.530569829018478</x:v>
       </x:c>
       <x:c r="M35" t="n">
-        <x:v>-2.530569829018478</x:v>
+        <x:v>6.026793670165464</x:v>
       </x:c>
       <x:c r="N35" t="n">
-        <x:v>6.026793670165464</x:v>
+        <x:v>0.8751753580596857</x:v>
       </x:c>
       <x:c r="O35" t="n">
-        <x:v>0.8751753580596857</x:v>
-      </x:c>
-      <x:c r="P35" t="n">
         <x:v>50.36034885942721</x:v>
       </x:c>
+      <x:c r="P35" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q35" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R35" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">fit error above 10% of the radius</x:t>
         </x:is>
       </x:c>
+      <x:c r="R35"/>
       <x:c r="S35"/>
       <x:c r="T35"/>
-      <x:c r="U35"/>
-      <x:c r="V35" t="b">
-        <x:v>1</x:v>
+      <x:c r="U35" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V35" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W35" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X35" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="inlineStr">
@@ -3186,68 +3138,66 @@
         </x:is>
       </x:c>
       <x:c r="D36" t="n">
-        <x:v>60</x:v>
+        <x:v>32.2117223739624</x:v>
       </x:c>
       <x:c r="E36" t="n">
-        <x:v>32.2117223739624</x:v>
+        <x:v>18.36134433746338</x:v>
       </x:c>
       <x:c r="F36" t="n">
-        <x:v>18.36134433746338</x:v>
+        <x:v>17.25013017654419</x:v>
       </x:c>
       <x:c r="G36" t="n">
-        <x:v>17.25013017654419</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H36" t="n">
-        <x:v>126</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I36" t="n">
-        <x:v>107</x:v>
+        <x:v>7.110270543663109</x:v>
       </x:c>
       <x:c r="J36" t="n">
-        <x:v>7.110270543663109</x:v>
+        <x:v>4.085384975425412</x:v>
       </x:c>
       <x:c r="K36" t="n">
-        <x:v>4.085384975425412</x:v>
+        <x:v>0.2447749737210188</x:v>
       </x:c>
       <x:c r="L36" t="n">
-        <x:v>0.2447749737210188</x:v>
+        <x:v>-1.962261061784088</x:v>
       </x:c>
       <x:c r="M36" t="n">
-        <x:v>-1.962261061784088</x:v>
+        <x:v>-4.790342710828583</x:v>
       </x:c>
       <x:c r="N36" t="n">
-        <x:v>-4.790342710828583</x:v>
+        <x:v>0.4550243964308177</x:v>
       </x:c>
       <x:c r="O36" t="n">
-        <x:v>0.4550243964308177</x:v>
-      </x:c>
-      <x:c r="P36" t="n">
         <x:v>50.11794211011614</x:v>
       </x:c>
-      <x:c r="Q36" t="inlineStr">
+      <x:c r="P36" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R36"/>
+      <x:c r="Q36"/>
+      <x:c r="R36" t="n">
+        <x:v>3.640254829219877</x:v>
+      </x:c>
       <x:c r="S36" t="n">
-        <x:v>3.640254829219877</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="T36" t="n">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="U36" t="n">
         <x:v>5.893019292365998</x:v>
       </x:c>
-      <x:c r="V36" t="b">
+      <x:c r="U36" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V36" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W36" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X36" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="X36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="inlineStr">
@@ -3266,68 +3216,66 @@
         </x:is>
       </x:c>
       <x:c r="D37" t="n">
-        <x:v>59</x:v>
+        <x:v>31.36538124084473</x:v>
       </x:c>
       <x:c r="E37" t="n">
-        <x:v>31.36538124084473</x:v>
+        <x:v>17.74437713623047</x:v>
       </x:c>
       <x:c r="F37" t="n">
-        <x:v>17.74437713623047</x:v>
+        <x:v>16.69107961654663</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>16.69107961654663</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>133</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:v>118</x:v>
+        <x:v>7.358007903909287</x:v>
       </x:c>
       <x:c r="J37" t="n">
-        <x:v>7.358007903909287</x:v>
+        <x:v>3.486935282408294</x:v>
       </x:c>
       <x:c r="K37" t="n">
-        <x:v>3.486935282408294</x:v>
+        <x:v>0.2867847892230847</x:v>
       </x:c>
       <x:c r="L37" t="n">
-        <x:v>0.2867847892230847</x:v>
+        <x:v>-2.553583177122971</x:v>
       </x:c>
       <x:c r="M37" t="n">
-        <x:v>-2.553583177122971</x:v>
+        <x:v>5.07395133318835</x:v>
       </x:c>
       <x:c r="N37" t="n">
-        <x:v>5.07395133318835</x:v>
+        <x:v>0.5992964403533607</x:v>
       </x:c>
       <x:c r="O37" t="n">
-        <x:v>0.5992964403533607</x:v>
-      </x:c>
-      <x:c r="P37" t="n">
         <x:v>50.23838061308763</x:v>
       </x:c>
-      <x:c r="Q37" t="inlineStr">
+      <x:c r="P37" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R37"/>
+      <x:c r="Q37"/>
+      <x:c r="R37" t="n">
+        <x:v>3.631445884685861</x:v>
+      </x:c>
       <x:c r="S37" t="n">
-        <x:v>3.631445884685861</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="T37" t="n">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="U37" t="n">
         <x:v>8.911410455044999</x:v>
       </x:c>
-      <x:c r="V37" t="b">
+      <x:c r="U37" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X37" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="X37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="inlineStr">
@@ -3346,62 +3294,60 @@
         </x:is>
       </x:c>
       <x:c r="D38" t="n">
-        <x:v>60</x:v>
+        <x:v>33.65160274505615</x:v>
       </x:c>
       <x:c r="E38" t="n">
-        <x:v>33.65160274505615</x:v>
+        <x:v>18.91727256774902</x:v>
       </x:c>
       <x:c r="F38" t="n">
-        <x:v>18.91727256774902</x:v>
+        <x:v>16.26697683334351</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>16.26697683334351</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>110</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:v>97</x:v>
+        <x:v>6.515081240448373</x:v>
       </x:c>
       <x:c r="J38" t="n">
-        <x:v>6.515081240448373</x:v>
+        <x:v>3.455707627008681</x:v>
       </x:c>
       <x:c r="K38" t="n">
-        <x:v>3.455707627008681</x:v>
+        <x:v>0.2893763327037064</x:v>
       </x:c>
       <x:c r="L38" t="n">
-        <x:v>0.2893763327037064</x:v>
+        <x:v>-1.797739993774567</x:v>
       </x:c>
       <x:c r="M38" t="n">
-        <x:v>-1.797739993774567</x:v>
+        <x:v>-4.113423927663584</x:v>
       </x:c>
       <x:c r="N38" t="n">
-        <x:v>-4.113423927663584</x:v>
+        <x:v>0.7246602010550836</x:v>
       </x:c>
       <x:c r="O38" t="n">
-        <x:v>0.7246602010550836</x:v>
-      </x:c>
-      <x:c r="P38" t="n">
         <x:v>51.81102625769082</x:v>
       </x:c>
-      <x:c r="Q38" t="inlineStr">
+      <x:c r="P38" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q38"/>
       <x:c r="R38"/>
       <x:c r="S38"/>
       <x:c r="T38"/>
-      <x:c r="U38"/>
-      <x:c r="V38" t="b">
+      <x:c r="U38" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V38" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X38" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="X38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="inlineStr">
@@ -3420,68 +3366,66 @@
         </x:is>
       </x:c>
       <x:c r="D39" t="n">
-        <x:v>59</x:v>
+        <x:v>29.38134288787842</x:v>
       </x:c>
       <x:c r="E39" t="n">
-        <x:v>29.38134288787842</x:v>
+        <x:v>17.08881664276123</x:v>
       </x:c>
       <x:c r="F39" t="n">
-        <x:v>17.08881664276123</x:v>
+        <x:v>15.73761749267578</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>15.73761749267578</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I39" t="n">
+        <x:v>7.466574058495417</x:v>
+      </x:c>
+      <x:c r="J39" t="n">
+        <x:v>3.476074144050049</x:v>
+      </x:c>
+      <x:c r="K39" t="n">
+        <x:v>0.287680860234724</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>-3.330208458648354</x:v>
+      </x:c>
+      <x:c r="M39" t="n">
+        <x:v>5.769987930072443</x:v>
+      </x:c>
+      <x:c r="N39" t="n">
+        <x:v>0.385464735998893</x:v>
+      </x:c>
+      <x:c r="O39" t="n">
+        <x:v>48.39949679997928</x:v>
+      </x:c>
+      <x:c r="P39" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q39"/>
+      <x:c r="R39" t="n">
+        <x:v>3.975862302111666</x:v>
+      </x:c>
+      <x:c r="S39" t="n">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="J39" t="n">
-        <x:v>7.466574058495417</x:v>
-      </x:c>
-      <x:c r="K39" t="n">
-        <x:v>3.476074144050049</x:v>
-      </x:c>
-      <x:c r="L39" t="n">
-        <x:v>0.287680860234724</x:v>
-      </x:c>
-      <x:c r="M39" t="n">
-        <x:v>-3.330208458648354</x:v>
-      </x:c>
-      <x:c r="N39" t="n">
-        <x:v>5.769987930072443</x:v>
-      </x:c>
-      <x:c r="O39" t="n">
-        <x:v>0.385464735998893</x:v>
-      </x:c>
-      <x:c r="P39" t="n">
-        <x:v>48.39949679997928</x:v>
-      </x:c>
-      <x:c r="Q39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">yes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R39"/>
-      <x:c r="S39" t="n">
-        <x:v>3.975862302111666</x:v>
-      </x:c>
       <x:c r="T39" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="U39" t="n">
         <x:v>10.42520685996307</x:v>
       </x:c>
-      <x:c r="V39" t="b">
+      <x:c r="U39" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V39" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W39" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X39" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="X39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="inlineStr">
@@ -3500,72 +3444,70 @@
         </x:is>
       </x:c>
       <x:c r="D40" t="n">
+        <x:v>38.83596420288086</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>16.07199096679688</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>17.28936958312988</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E40" t="n">
-        <x:v>38.83596420288086</x:v>
-      </x:c>
-      <x:c r="F40" t="n">
-        <x:v>16.07199096679688</x:v>
-      </x:c>
-      <x:c r="G40" t="n">
-        <x:v>17.28936958312988</x:v>
-      </x:c>
       <x:c r="H40" t="n">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:v>34</x:v>
+        <x:v>5.784103919139367</x:v>
       </x:c>
       <x:c r="J40" t="n">
-        <x:v>5.784103919139367</x:v>
+        <x:v>2.543792860442394</x:v>
       </x:c>
       <x:c r="K40" t="n">
-        <x:v>2.543792860442394</x:v>
+        <x:v>0.3931137694230687</x:v>
       </x:c>
       <x:c r="L40" t="n">
-        <x:v>0.3931137694230687</x:v>
+        <x:v>-1.32469722531234</x:v>
       </x:c>
       <x:c r="M40" t="n">
-        <x:v>-1.32469722531234</x:v>
+        <x:v>5.445999347192649</x:v>
       </x:c>
       <x:c r="N40" t="n">
-        <x:v>5.445999347192649</x:v>
+        <x:v>0.939345887915467</x:v>
       </x:c>
       <x:c r="O40" t="n">
-        <x:v>0.939345887915467</x:v>
-      </x:c>
-      <x:c r="P40" t="n">
         <x:v>65.50273309193719</x:v>
       </x:c>
+      <x:c r="P40" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q40" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R40" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">sphere centre within 5% of the edge of the search band; fewer than 40 inliers</x:t>
         </x:is>
       </x:c>
+      <x:c r="R40" t="n">
+        <x:v>2.432620947668183</x:v>
+      </x:c>
       <x:c r="S40" t="n">
-        <x:v>2.432620947668183</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="T40" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="U40" t="n">
         <x:v>4.115753745604573</x:v>
       </x:c>
-      <x:c r="V40" t="b">
+      <x:c r="U40" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W40" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X40" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="inlineStr">
@@ -3584,72 +3526,70 @@
         </x:is>
       </x:c>
       <x:c r="D41" t="n">
-        <x:v>55</x:v>
+        <x:v>41.58774280548096</x:v>
       </x:c>
       <x:c r="E41" t="n">
-        <x:v>41.58774280548096</x:v>
+        <x:v>16.33449840545654</x:v>
       </x:c>
       <x:c r="F41" t="n">
-        <x:v>16.33449840545654</x:v>
+        <x:v>13.52271699905396</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>13.52271699905396</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H41" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I41" t="n">
+        <x:v>2.856251279186675</x:v>
+      </x:c>
+      <x:c r="J41" t="n">
+        <x:v>3.615468501154491</x:v>
+      </x:c>
+      <x:c r="K41" t="n">
+        <x:v>0.2765893271316512</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>0.07596107453680481</x:v>
+      </x:c>
+      <x:c r="M41" t="n">
+        <x:v>5.945805582834584</x:v>
+      </x:c>
+      <x:c r="N41" t="n">
+        <x:v>1.170316288796121</x:v>
+      </x:c>
+      <x:c r="O41" t="n">
+        <x:v>70.89750384429922</x:v>
+      </x:c>
+      <x:c r="P41" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q41" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sphere centre within 5% of the edge of the search band; fewer than 40 inliers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R41" t="n">
+        <x:v>2.973195611984072</x:v>
+      </x:c>
+      <x:c r="S41" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="I41" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J41" t="n">
-        <x:v>2.856251279186675</x:v>
-      </x:c>
-      <x:c r="K41" t="n">
-        <x:v>3.615468501154491</x:v>
-      </x:c>
-      <x:c r="L41" t="n">
-        <x:v>0.2765893271316512</x:v>
-      </x:c>
-      <x:c r="M41" t="n">
-        <x:v>0.07596107453680481</x:v>
-      </x:c>
-      <x:c r="N41" t="n">
-        <x:v>5.945805582834584</x:v>
-      </x:c>
-      <x:c r="O41" t="n">
-        <x:v>1.170316288796121</x:v>
-      </x:c>
-      <x:c r="P41" t="n">
-        <x:v>70.89750384429922</x:v>
-      </x:c>
-      <x:c r="Q41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sphere centre within 5% of the edge of the search band; fewer than 40 inliers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S41" t="n">
-        <x:v>2.973195611984072</x:v>
-      </x:c>
       <x:c r="T41" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="U41" t="n">
         <x:v>3.797942680635497</x:v>
       </x:c>
-      <x:c r="V41" t="b">
+      <x:c r="U41" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V41" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W41" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X41" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="inlineStr">
@@ -3668,72 +3608,70 @@
         </x:is>
       </x:c>
       <x:c r="D42" t="n">
-        <x:v>60</x:v>
+        <x:v>40.69521045684814</x:v>
       </x:c>
       <x:c r="E42" t="n">
-        <x:v>40.69521045684814</x:v>
+        <x:v>16.41843461990356</x:v>
       </x:c>
       <x:c r="F42" t="n">
-        <x:v>16.41843461990356</x:v>
+        <x:v>16.32512140274048</x:v>
       </x:c>
       <x:c r="G42" t="n">
-        <x:v>16.32512140274048</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H42" t="n">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:v>37</x:v>
+        <x:v>2.738585350031179</x:v>
       </x:c>
       <x:c r="J42" t="n">
-        <x:v>2.738585350031179</x:v>
+        <x:v>3.100094867465993</x:v>
       </x:c>
       <x:c r="K42" t="n">
-        <x:v>3.100094867465993</x:v>
+        <x:v>0.32257077371874</x:v>
       </x:c>
       <x:c r="L42" t="n">
-        <x:v>0.32257077371874</x:v>
+        <x:v>-0.9676666815453707</x:v>
       </x:c>
       <x:c r="M42" t="n">
-        <x:v>-0.9676666815453707</x:v>
+        <x:v>5.323008672001041</x:v>
       </x:c>
       <x:c r="N42" t="n">
-        <x:v>5.323008672001041</x:v>
+        <x:v>1.367816672437884</x:v>
       </x:c>
       <x:c r="O42" t="n">
-        <x:v>1.367816672437884</x:v>
-      </x:c>
-      <x:c r="P42" t="n">
         <x:v>66.58195997262909</x:v>
       </x:c>
+      <x:c r="P42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q42" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R42" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">sphere centre within 5% of the edge of the search band; fewer than 40 inliers</x:t>
         </x:is>
       </x:c>
+      <x:c r="R42" t="n">
+        <x:v>2.714032462747634</x:v>
+      </x:c>
       <x:c r="S42" t="n">
-        <x:v>2.714032462747634</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="T42" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="U42" t="n">
         <x:v>3.858115076740751</x:v>
       </x:c>
-      <x:c r="V42" t="b">
+      <x:c r="U42" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V42" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W42" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X42" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="inlineStr">
@@ -3752,66 +3690,64 @@
         </x:is>
       </x:c>
       <x:c r="D43" t="n">
-        <x:v>75</x:v>
+        <x:v>37.0435676574707</x:v>
       </x:c>
       <x:c r="E43" t="n">
-        <x:v>37.0435676574707</x:v>
+        <x:v>15.68787813186646</x:v>
       </x:c>
       <x:c r="F43" t="n">
-        <x:v>15.68787813186646</x:v>
+        <x:v>13.34999465942383</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>13.34999465942383</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:v>19</x:v>
+        <x:v>0.9348169433331677</x:v>
       </x:c>
       <x:c r="J43" t="n">
-        <x:v>0.9348169433331677</x:v>
+        <x:v>3.994806238179539</x:v>
       </x:c>
       <x:c r="K43" t="n">
-        <x:v>3.994806238179539</x:v>
+        <x:v>0.2503250321486699</x:v>
       </x:c>
       <x:c r="L43" t="n">
-        <x:v>0.2503250321486699</x:v>
+        <x:v>2.421296025151534</x:v>
       </x:c>
       <x:c r="M43" t="n">
-        <x:v>2.421296025151534</x:v>
+        <x:v>-4.590261058840746</x:v>
       </x:c>
       <x:c r="N43" t="n">
-        <x:v>-4.590261058840746</x:v>
+        <x:v>1.398216905721528</x:v>
       </x:c>
       <x:c r="O43" t="n">
-        <x:v>1.398216905721528</x:v>
-      </x:c>
-      <x:c r="P43" t="n">
         <x:v>74.09019865735715</x:v>
       </x:c>
+      <x:c r="P43" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">flagged</x:t>
+        </x:is>
+      </x:c>
       <x:c r="Q43" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">flagged</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R43" t="inlineStr">
-        <x:is>
           <x:t xml:space="preserve">sphere centre within 5% of the edge of the search band; fewer than 40 inliers</x:t>
         </x:is>
       </x:c>
+      <x:c r="R43"/>
       <x:c r="S43"/>
       <x:c r="T43"/>
-      <x:c r="U43"/>
-      <x:c r="V43" t="b">
+      <x:c r="U43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V43" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W43" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X43" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="inlineStr">
@@ -3830,62 +3766,60 @@
         </x:is>
       </x:c>
       <x:c r="D44" t="n">
-        <x:v>60</x:v>
+        <x:v>27.24489116668701</x:v>
       </x:c>
       <x:c r="E44" t="n">
-        <x:v>27.24489116668701</x:v>
+        <x:v>15.21861791610718</x:v>
       </x:c>
       <x:c r="F44" t="n">
-        <x:v>15.21861791610718</x:v>
+        <x:v>14.60830450057983</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>14.60830450057983</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>88</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:v>76</x:v>
+        <x:v>3.240403577821636</x:v>
       </x:c>
       <x:c r="J44" t="n">
-        <x:v>3.240403577821636</x:v>
+        <x:v>3.175272140023995</x:v>
       </x:c>
       <x:c r="K44" t="n">
-        <x:v>3.175272140023995</x:v>
+        <x:v>0.3149336358906368</x:v>
       </x:c>
       <x:c r="L44" t="n">
-        <x:v>0.3149336358906368</x:v>
+        <x:v>-3.461916097470704</x:v>
       </x:c>
       <x:c r="M44" t="n">
-        <x:v>-3.461916097470704</x:v>
+        <x:v>-3.697555905397272</x:v>
       </x:c>
       <x:c r="N44" t="n">
-        <x:v>-3.697555905397272</x:v>
+        <x:v>1.857108292055113</x:v>
       </x:c>
       <x:c r="O44" t="n">
-        <x:v>1.857108292055113</x:v>
-      </x:c>
-      <x:c r="P44" t="n">
         <x:v>50.49269355904297</x:v>
       </x:c>
-      <x:c r="Q44" t="inlineStr">
+      <x:c r="P44" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q44"/>
       <x:c r="R44"/>
       <x:c r="S44"/>
       <x:c r="T44"/>
-      <x:c r="U44"/>
-      <x:c r="V44" t="b">
-        <x:v>1</x:v>
+      <x:c r="U44" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V44" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W44" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X44" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="inlineStr">
@@ -3904,68 +3838,66 @@
         </x:is>
       </x:c>
       <x:c r="D45" t="n">
-        <x:v>60</x:v>
+        <x:v>27.97867488861084</x:v>
       </x:c>
       <x:c r="E45" t="n">
-        <x:v>27.97867488861084</x:v>
+        <x:v>15.26332521438599</x:v>
       </x:c>
       <x:c r="F45" t="n">
-        <x:v>15.26332521438599</x:v>
+        <x:v>15.14688491821289</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>15.14688491821289</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H45" t="n">
-        <x:v>113</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:v>97</x:v>
+        <x:v>4.063350851733255</x:v>
       </x:c>
       <x:c r="J45" t="n">
-        <x:v>4.063350851733255</x:v>
+        <x:v>3.444025533210048</x:v>
       </x:c>
       <x:c r="K45" t="n">
-        <x:v>3.444025533210048</x:v>
+        <x:v>0.2903578937952696</x:v>
       </x:c>
       <x:c r="L45" t="n">
-        <x:v>0.2903578937952696</x:v>
+        <x:v>-3.945825947507462</x:v>
       </x:c>
       <x:c r="M45" t="n">
-        <x:v>-3.945825947507462</x:v>
+        <x:v>5.117205296023566</x:v>
       </x:c>
       <x:c r="N45" t="n">
-        <x:v>5.117205296023566</x:v>
+        <x:v>0.2947904118780514</x:v>
       </x:c>
       <x:c r="O45" t="n">
-        <x:v>0.2947904118780514</x:v>
-      </x:c>
-      <x:c r="P45" t="n">
         <x:v>51.68637957778591</x:v>
       </x:c>
-      <x:c r="Q45" t="inlineStr">
+      <x:c r="P45" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R45"/>
+      <x:c r="Q45"/>
+      <x:c r="R45" t="n">
+        <x:v>3.372612061844032</x:v>
+      </x:c>
       <x:c r="S45" t="n">
-        <x:v>3.372612061844032</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="T45" t="n">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="U45" t="n">
         <x:v>3.078473430281802</x:v>
       </x:c>
-      <x:c r="V45" t="b">
+      <x:c r="U45" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W45" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X45" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="X45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="inlineStr">
@@ -3984,68 +3916,66 @@
         </x:is>
       </x:c>
       <x:c r="D46" t="n">
-        <x:v>60</x:v>
+        <x:v>29.2781867980957</x:v>
       </x:c>
       <x:c r="E46" t="n">
-        <x:v>29.2781867980957</x:v>
+        <x:v>17.26843738555908</x:v>
       </x:c>
       <x:c r="F46" t="n">
-        <x:v>17.26843738555908</x:v>
+        <x:v>15.36229848861694</x:v>
       </x:c>
       <x:c r="G46" t="n">
-        <x:v>15.36229848861694</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H46" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>6.19858657080853</x:v>
+      </x:c>
+      <x:c r="J46" t="n">
+        <x:v>3.204961906603487</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
+        <x:v>0.3120161890035589</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>0.02565909293877559</x:v>
+      </x:c>
+      <x:c r="M46" t="n">
+        <x:v>4.674891077557215</x:v>
+      </x:c>
+      <x:c r="N46" t="n">
+        <x:v>0.2963491477424369</x:v>
+      </x:c>
+      <x:c r="O46" t="n">
+        <x:v>49.98288787677638</x:v>
+      </x:c>
+      <x:c r="P46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q46"/>
+      <x:c r="R46" t="n">
+        <x:v>3.46753445756775</x:v>
+      </x:c>
+      <x:c r="S46" t="n">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="I46" t="n">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="J46" t="n">
-        <x:v>6.19858657080853</x:v>
-      </x:c>
-      <x:c r="K46" t="n">
-        <x:v>3.204961906603487</x:v>
-      </x:c>
-      <x:c r="L46" t="n">
-        <x:v>0.3120161890035589</x:v>
-      </x:c>
-      <x:c r="M46" t="n">
-        <x:v>0.02565909293877559</x:v>
-      </x:c>
-      <x:c r="N46" t="n">
-        <x:v>4.674891077557215</x:v>
-      </x:c>
-      <x:c r="O46" t="n">
-        <x:v>0.2963491477424369</x:v>
-      </x:c>
-      <x:c r="P46" t="n">
-        <x:v>49.98288787677638</x:v>
-      </x:c>
-      <x:c r="Q46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">yes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R46"/>
-      <x:c r="S46" t="n">
-        <x:v>3.46753445756775</x:v>
-      </x:c>
       <x:c r="T46" t="n">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="U46" t="n">
         <x:v>6.911693127750863</x:v>
       </x:c>
-      <x:c r="V46" t="b">
-        <x:v>1</x:v>
+      <x:c r="U46" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V46" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W46" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X46" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="X46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="inlineStr">
@@ -4064,68 +3994,66 @@
         </x:is>
       </x:c>
       <x:c r="D47" t="n">
-        <x:v>59</x:v>
+        <x:v>29.18683528900146</x:v>
       </x:c>
       <x:c r="E47" t="n">
-        <x:v>29.18683528900146</x:v>
+        <x:v>16.83408498764038</x:v>
       </x:c>
       <x:c r="F47" t="n">
-        <x:v>16.83408498764038</x:v>
+        <x:v>14.75949335098267</x:v>
       </x:c>
       <x:c r="G47" t="n">
-        <x:v>14.75949335098267</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H47" t="n">
-        <x:v>130</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:v>116</x:v>
+        <x:v>7.293057452075836</x:v>
       </x:c>
       <x:c r="J47" t="n">
-        <x:v>7.293057452075836</x:v>
+        <x:v>4.628349461829738</x:v>
       </x:c>
       <x:c r="K47" t="n">
-        <x:v>4.628349461829738</x:v>
+        <x:v>0.2160597440290663</x:v>
       </x:c>
       <x:c r="L47" t="n">
-        <x:v>0.2160597440290663</x:v>
+        <x:v>0.4856907592225654</x:v>
       </x:c>
       <x:c r="M47" t="n">
-        <x:v>0.4856907592225654</x:v>
+        <x:v>4.595283291680136</x:v>
       </x:c>
       <x:c r="N47" t="n">
-        <x:v>4.595283291680136</x:v>
+        <x:v>4.128346322311304</x:v>
       </x:c>
       <x:c r="O47" t="n">
-        <x:v>4.128346322311304</x:v>
-      </x:c>
-      <x:c r="P47" t="n">
         <x:v>50.94018883603849</x:v>
       </x:c>
-      <x:c r="Q47" t="inlineStr">
+      <x:c r="P47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R47"/>
+      <x:c r="Q47"/>
+      <x:c r="R47" t="n">
+        <x:v>3.515835764632162</x:v>
+      </x:c>
       <x:c r="S47" t="n">
-        <x:v>3.515835764632162</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="T47" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="U47" t="n">
         <x:v>2.836590679761768</x:v>
       </x:c>
-      <x:c r="V47" t="b">
+      <x:c r="U47" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V47" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X47" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="inlineStr">
@@ -4144,62 +4072,60 @@
         </x:is>
       </x:c>
       <x:c r="D48" t="n">
-        <x:v>60</x:v>
+        <x:v>29.75191783905029</x:v>
       </x:c>
       <x:c r="E48" t="n">
-        <x:v>29.75191783905029</x:v>
+        <x:v>16.84795093536377</x:v>
       </x:c>
       <x:c r="F48" t="n">
-        <x:v>16.84795093536377</x:v>
+        <x:v>14.28117418289185</x:v>
       </x:c>
       <x:c r="G48" t="n">
-        <x:v>14.28117418289185</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H48" t="n">
-        <x:v>94</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:v>77</x:v>
+        <x:v>2.537678633883192</x:v>
       </x:c>
       <x:c r="J48" t="n">
-        <x:v>2.537678633883192</x:v>
+        <x:v>3.44448176345399</x:v>
       </x:c>
       <x:c r="K48" t="n">
-        <x:v>3.44448176345399</x:v>
+        <x:v>0.2903194351643887</x:v>
       </x:c>
       <x:c r="L48" t="n">
-        <x:v>0.2903194351643887</x:v>
+        <x:v>1.432273554155349</x:v>
       </x:c>
       <x:c r="M48" t="n">
-        <x:v>1.432273554155349</x:v>
+        <x:v>8.90757540447999</x:v>
       </x:c>
       <x:c r="N48" t="n">
-        <x:v>8.90757540447999</x:v>
+        <x:v>1.993583479356905</x:v>
       </x:c>
       <x:c r="O48" t="n">
-        <x:v>1.993583479356905</x:v>
-      </x:c>
-      <x:c r="P48" t="n">
         <x:v>50.99820401629034</x:v>
       </x:c>
-      <x:c r="Q48" t="inlineStr">
+      <x:c r="P48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
+      <x:c r="Q48"/>
       <x:c r="R48"/>
       <x:c r="S48"/>
       <x:c r="T48"/>
-      <x:c r="U48"/>
-      <x:c r="V48" t="b">
+      <x:c r="U48" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V48" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W48" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X48" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="X48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="inlineStr">
@@ -4218,68 +4144,66 @@
         </x:is>
       </x:c>
       <x:c r="D49" t="n">
-        <x:v>55</x:v>
+        <x:v>29.69509029388428</x:v>
       </x:c>
       <x:c r="E49" t="n">
-        <x:v>29.69509029388428</x:v>
+        <x:v>17.53605604171753</x:v>
       </x:c>
       <x:c r="F49" t="n">
-        <x:v>17.53605604171753</x:v>
+        <x:v>15.33406496047974</x:v>
       </x:c>
       <x:c r="G49" t="n">
-        <x:v>15.33406496047974</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H49" t="n">
-        <x:v>128</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:v>113</x:v>
+        <x:v>4.104976167090806</x:v>
       </x:c>
       <x:c r="J49" t="n">
-        <x:v>4.104976167090806</x:v>
+        <x:v>2.778433607517852</x:v>
       </x:c>
       <x:c r="K49" t="n">
-        <x:v>2.778433607517852</x:v>
+        <x:v>0.3599150245282854</x:v>
       </x:c>
       <x:c r="L49" t="n">
-        <x:v>0.3599150245282854</x:v>
+        <x:v>-5.410034929596837</x:v>
       </x:c>
       <x:c r="M49" t="n">
-        <x:v>-5.410034929596837</x:v>
+        <x:v>3.255374877633139</x:v>
       </x:c>
       <x:c r="N49" t="n">
-        <x:v>3.255374877633139</x:v>
+        <x:v>2.295661030834171</x:v>
       </x:c>
       <x:c r="O49" t="n">
-        <x:v>2.295661030834171</x:v>
-      </x:c>
-      <x:c r="P49" t="n">
         <x:v>50.33154080466959</x:v>
       </x:c>
-      <x:c r="Q49" t="inlineStr">
+      <x:c r="P49" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R49"/>
+      <x:c r="Q49"/>
+      <x:c r="R49" t="n">
+        <x:v>3.099491384956314</x:v>
+      </x:c>
       <x:c r="S49" t="n">
-        <x:v>3.099491384956314</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="T49" t="n">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="U49" t="n">
         <x:v>8.290858819303002</x:v>
       </x:c>
-      <x:c r="V49" t="b">
-        <x:v>1</x:v>
+      <x:c r="U49" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V49" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W49" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X49" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="inlineStr">
@@ -4298,68 +4222,66 @@
         </x:is>
       </x:c>
       <x:c r="D50" t="n">
-        <x:v>60</x:v>
+        <x:v>36.59341621398926</x:v>
       </x:c>
       <x:c r="E50" t="n">
-        <x:v>36.59341621398926</x:v>
+        <x:v>20.88001346588135</x:v>
       </x:c>
       <x:c r="F50" t="n">
-        <x:v>20.88001346588135</x:v>
+        <x:v>19.65026903152466</x:v>
       </x:c>
       <x:c r="G50" t="n">
-        <x:v>19.65026903152466</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H50" t="n">
-        <x:v>51</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:v>42</x:v>
+        <x:v>3.594187800864754</x:v>
       </x:c>
       <x:c r="J50" t="n">
-        <x:v>3.594187800864754</x:v>
+        <x:v>4.490272860486622</x:v>
       </x:c>
       <x:c r="K50" t="n">
-        <x:v>4.490272860486622</x:v>
+        <x:v>0.2227036153637282</x:v>
       </x:c>
       <x:c r="L50" t="n">
-        <x:v>0.2227036153637282</x:v>
+        <x:v>0.186099948280202</x:v>
       </x:c>
       <x:c r="M50" t="n">
-        <x:v>0.186099948280202</x:v>
+        <x:v>1.71274668812425</x:v>
       </x:c>
       <x:c r="N50" t="n">
-        <x:v>1.71274668812425</x:v>
+        <x:v>4.253036560331958</x:v>
       </x:c>
       <x:c r="O50" t="n">
-        <x:v>4.253036560331958</x:v>
-      </x:c>
-      <x:c r="P50" t="n">
         <x:v>50.59132957040569</x:v>
       </x:c>
-      <x:c r="Q50" t="inlineStr">
+      <x:c r="P50" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R50"/>
+      <x:c r="Q50"/>
+      <x:c r="R50" t="n">
+        <x:v>4.187848136636668</x:v>
+      </x:c>
       <x:c r="S50" t="n">
-        <x:v>4.187848136636668</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T50" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="U50" t="n">
         <x:v>3.217558925863514</x:v>
       </x:c>
-      <x:c r="V50" t="b">
+      <x:c r="U50" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V50" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X50" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="inlineStr">
@@ -4378,68 +4300,66 @@
         </x:is>
       </x:c>
       <x:c r="D51" t="n">
-        <x:v>60</x:v>
+        <x:v>36.57126808166504</x:v>
       </x:c>
       <x:c r="E51" t="n">
-        <x:v>36.57126808166504</x:v>
+        <x:v>20.8926887512207</x:v>
       </x:c>
       <x:c r="F51" t="n">
-        <x:v>20.8926887512207</x:v>
+        <x:v>19.73353958129883</x:v>
       </x:c>
       <x:c r="G51" t="n">
-        <x:v>19.73353958129883</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H51" t="n">
-        <x:v>156</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:v>138</x:v>
+        <x:v>4.383309291825928</x:v>
       </x:c>
       <x:c r="J51" t="n">
-        <x:v>4.383309291825928</x:v>
+        <x:v>4.717264921616263</x:v>
       </x:c>
       <x:c r="K51" t="n">
-        <x:v>4.717264921616263</x:v>
+        <x:v>0.2119872461301946</x:v>
       </x:c>
       <x:c r="L51" t="n">
-        <x:v>0.2119872461301946</x:v>
+        <x:v>-3.573768643230887</x:v>
       </x:c>
       <x:c r="M51" t="n">
-        <x:v>-3.573768643230887</x:v>
+        <x:v>-5.766361986701065</x:v>
       </x:c>
       <x:c r="N51" t="n">
-        <x:v>-5.766361986701065</x:v>
+        <x:v>2.52628475432867</x:v>
       </x:c>
       <x:c r="O51" t="n">
-        <x:v>2.52628475432867</x:v>
-      </x:c>
-      <x:c r="P51" t="n">
         <x:v>53.42484457148528</x:v>
       </x:c>
-      <x:c r="Q51" t="inlineStr">
+      <x:c r="P51" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R51"/>
+      <x:c r="Q51"/>
+      <x:c r="R51" t="n">
+        <x:v>4.669385441520716</x:v>
+      </x:c>
       <x:c r="S51" t="n">
-        <x:v>4.669385441520716</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="T51" t="n">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="U51" t="n">
         <x:v>4.537292113196781</x:v>
       </x:c>
-      <x:c r="V51" t="b">
+      <x:c r="U51" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V51" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X51" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="X51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="inlineStr">
@@ -4458,68 +4378,66 @@
         </x:is>
       </x:c>
       <x:c r="D52" t="n">
-        <x:v>59</x:v>
+        <x:v>28.16117572784424</x:v>
       </x:c>
       <x:c r="E52" t="n">
-        <x:v>28.16117572784424</x:v>
+        <x:v>16.88805198669434</x:v>
       </x:c>
       <x:c r="F52" t="n">
-        <x:v>16.88805198669434</x:v>
+        <x:v>16.20902538299561</x:v>
       </x:c>
       <x:c r="G52" t="n">
-        <x:v>16.20902538299561</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H52" t="n">
-        <x:v>116</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:v>98</x:v>
+        <x:v>4.381483517367886</x:v>
       </x:c>
       <x:c r="J52" t="n">
-        <x:v>4.381483517367886</x:v>
+        <x:v>3.479959228426322</x:v>
       </x:c>
       <x:c r="K52" t="n">
-        <x:v>3.479959228426322</x:v>
+        <x:v>0.2873596885364119</x:v>
       </x:c>
       <x:c r="L52" t="n">
-        <x:v>0.2873596885364119</x:v>
+        <x:v>-4.065796241367945</x:v>
       </x:c>
       <x:c r="M52" t="n">
-        <x:v>-4.065796241367945</x:v>
+        <x:v>-4.49204156341337</x:v>
       </x:c>
       <x:c r="N52" t="n">
-        <x:v>-4.49204156341337</x:v>
+        <x:v>1.144327094842741</x:v>
       </x:c>
       <x:c r="O52" t="n">
-        <x:v>1.144327094842741</x:v>
-      </x:c>
-      <x:c r="P52" t="n">
         <x:v>48.22788952324257</x:v>
       </x:c>
-      <x:c r="Q52" t="inlineStr">
+      <x:c r="P52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="R52"/>
+      <x:c r="Q52"/>
+      <x:c r="R52" t="n">
+        <x:v>3.58532363752286</x:v>
+      </x:c>
       <x:c r="S52" t="n">
-        <x:v>3.58532363752286</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="T52" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="U52" t="n">
         <x:v>4.260446987905302</x:v>
       </x:c>
-      <x:c r="V52" t="b">
+      <x:c r="U52" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V52" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W52" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X52" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="X52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="inlineStr">
@@ -4537,67 +4455,43 @@
           <x:t xml:space="preserve">Peromyscus gossypinus</x:t>
         </x:is>
       </x:c>
-      <x:c r="D53"/>
+      <x:c r="D53" t="n">
+        <x:v>28.942147553046645</x:v>
+      </x:c>
       <x:c r="E53" t="n">
-        <x:v>28.942147553046645</x:v>
+        <x:v>14.090034107395692</x:v>
       </x:c>
       <x:c r="F53" t="n">
-        <x:v>14.090034107395692</x:v>
-      </x:c>
-      <x:c r="G53" t="n">
         <x:v>14.930267714146463</x:v>
       </x:c>
-      <x:c r="H53" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="I53" t="n">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="J53" t="n">
-        <x:v>11.177557813910838</x:v>
-      </x:c>
-      <x:c r="K53" t="n">
-        <x:v>4.652474008804686</x:v>
-      </x:c>
-      <x:c r="L53" t="n">
-        <x:v>0.214939406025166</x:v>
-      </x:c>
-      <x:c r="M53" t="n">
-        <x:v>3.925786424662138</x:v>
-      </x:c>
-      <x:c r="N53" t="n">
-        <x:v>-0.098679446597609</x:v>
-      </x:c>
-      <x:c r="O53" t="n">
-        <x:v>-0.033302924742653</x:v>
-      </x:c>
-      <x:c r="P53" t="n">
-        <x:v>56.038952439608956</x:v>
-      </x:c>
-      <x:c r="Q53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">no fit reported</x:t>
-        </x:is>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
+      <x:c r="I53"/>
+      <x:c r="J53"/>
+      <x:c r="K53"/>
+      <x:c r="L53"/>
+      <x:c r="M53"/>
+      <x:c r="N53"/>
+      <x:c r="O53"/>
+      <x:c r="P53" t="str">
+        <x:v>no fit reported</x:v>
+      </x:c>
+      <x:c r="Q53" t="str">
+        <x:v>The fitted sphere does not identify the orbit; no orbital measurements are reported.</x:v>
       </x:c>
       <x:c r="R53"/>
-      <x:c r="S53" t="n">
-        <x:v>4.420446213415516</x:v>
-      </x:c>
-      <x:c r="T53" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="U53" t="n">
-        <x:v>10.345832691531601</x:v>
-      </x:c>
-      <x:c r="V53" t="b">
-        <x:v>1</x:v>
+      <x:c r="S53"/>
+      <x:c r="T53"/>
+      <x:c r="U53" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V53" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W53" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X53" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="X53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
@@ -4611,67 +4505,43 @@
       <x:c r="C54" t="str">
         <x:v>Peromyscus simulus</x:v>
       </x:c>
-      <x:c r="D54"/>
+      <x:c r="D54" t="n">
+        <x:v>28.81913728717502</x:v>
+      </x:c>
       <x:c r="E54" t="n">
-        <x:v>28.81913728717502</x:v>
+        <x:v>14.735478628480262</x:v>
       </x:c>
       <x:c r="F54" t="n">
-        <x:v>14.735478628480262</x:v>
-      </x:c>
-      <x:c r="G54" t="n">
         <x:v>15.64310965977333</x:v>
       </x:c>
-      <x:c r="H54" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="I54" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J54" t="n">
-        <x:v>4.24053856800054</x:v>
-      </x:c>
-      <x:c r="K54" t="n">
-        <x:v>2.041778687652857</x:v>
-      </x:c>
-      <x:c r="L54" t="n">
-        <x:v>0.489769046002512</x:v>
-      </x:c>
-      <x:c r="M54" t="n">
-        <x:v>-0.409297638243933</x:v>
-      </x:c>
-      <x:c r="N54" t="n">
-        <x:v>5.647867949002236</x:v>
-      </x:c>
-      <x:c r="O54" t="n">
-        <x:v>0.607128751456948</x:v>
-      </x:c>
-      <x:c r="P54" t="n">
-        <x:v>44.490606234220536</x:v>
-      </x:c>
-      <x:c r="Q54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">no fit reported</x:t>
-        </x:is>
+      <x:c r="G54"/>
+      <x:c r="H54"/>
+      <x:c r="I54"/>
+      <x:c r="J54"/>
+      <x:c r="K54"/>
+      <x:c r="L54"/>
+      <x:c r="M54"/>
+      <x:c r="N54"/>
+      <x:c r="O54"/>
+      <x:c r="P54" t="str">
+        <x:v>no fit reported</x:v>
+      </x:c>
+      <x:c r="Q54" t="str">
+        <x:v>The fitted sphere does not identify the orbit; no orbital measurements are reported.</x:v>
       </x:c>
       <x:c r="R54"/>
-      <x:c r="S54" t="n">
-        <x:v>2.076603247102722</x:v>
-      </x:c>
-      <x:c r="T54" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="U54" t="n">
-        <x:v>6.596833094770825</x:v>
-      </x:c>
-      <x:c r="V54" t="b">
-        <x:v>1</x:v>
+      <x:c r="S54"/>
+      <x:c r="T54"/>
+      <x:c r="U54" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V54" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W54" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X54" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55"/>
